--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E2EC4A-AA69-4654-BCE9-20C84949F6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E31A9C1-FA6D-4FA1-BCC3-1CF719654E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="260">
   <si>
     <t>category</t>
   </si>
@@ -501,21 +501,6 @@
     <t>"base scenario"</t>
   </si>
   <si>
-    <t>preference</t>
-  </si>
-  <si>
-    <t>resilience premium</t>
-  </si>
-  <si>
-    <t>resilience_premium_2025</t>
-  </si>
-  <si>
-    <t>resilience_premium_2030</t>
-  </si>
-  <si>
-    <t>resilience_premium_2050</t>
-  </si>
-  <si>
     <t>euros</t>
   </si>
   <si>
@@ -735,12 +720,6 @@
     <t>wood stove or boiler efficiency</t>
   </si>
   <si>
-    <t>solid_fuel_system_efficiency</t>
-  </si>
-  <si>
-    <t>electricity_system_efficiency</t>
-  </si>
-  <si>
     <t>solid_fuel_system_lifetime</t>
   </si>
   <si>
@@ -928,13 +907,28 @@
   </si>
   <si>
     <t>heat_pump_cop_2010</t>
+  </si>
+  <si>
+    <t>solid_fuel_efficiency</t>
+  </si>
+  <si>
+    <t>electricity_efficiency</t>
+  </si>
+  <si>
+    <t>night usage of electric heating</t>
+  </si>
+  <si>
+    <t>night_rate_usage_factor</t>
+  </si>
+  <si>
+    <t>labour_cost_2005</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -946,20 +940,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -992,22 +972,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1039,27 +1009,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1090,20 +1045,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1119,30 +1071,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="7"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="20% - Accent1" xfId="4" builtinId="30"/>
-    <cellStyle name="20% - Accent2" xfId="5" builtinId="34"/>
-    <cellStyle name="20% - Accent3" xfId="6" builtinId="38"/>
-    <cellStyle name="20% - Accent4" xfId="7" builtinId="42"/>
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
-    <cellStyle name="Good" xfId="2" builtinId="26"/>
-    <cellStyle name="Input" xfId="1" builtinId="20"/>
+  <cellStyles count="6">
+    <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
+    <cellStyle name="20% - Accent2" xfId="3" builtinId="34"/>
+    <cellStyle name="20% - Accent3" xfId="4" builtinId="38"/>
+    <cellStyle name="20% - Accent4" xfId="5" builtinId="42"/>
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1465,115 +1415,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A1" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>137</v>
+      <c r="C3" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>132</v>
+      <c r="A4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="3"/>
+      <c r="A5" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
@@ -1581,35 +1531,35 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D14" t="s">
@@ -1617,57 +1567,57 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>111</v>
       </c>
       <c r="D19" t="s">
@@ -1675,13 +1625,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D20" t="s">
@@ -1689,46 +1639,46 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D24" t="s">
@@ -1736,13 +1686,13 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D25" t="s">
@@ -1750,118 +1700,118 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="3"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="3"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="3"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C38" t="s">
@@ -1869,15 +1819,15 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1888,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -1920,1061 +1870,1060 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="9">
+        <v>2196</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="9">
+        <v>16</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="10">
-        <v>2196</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="10">
-        <v>16</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="D4" s="13">
+        <v>30</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="12">
         <v>40</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E5" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="13">
+        <v>60</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="13">
+        <v>60</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="10">
+        <v>700</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="14">
-        <v>60</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="14">
-        <v>60</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="C12" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="15">
-        <v>60</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="D12" s="12">
         <v>150</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="11">
-        <v>700</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="11">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="E12" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D13" s="13">
+        <v>130</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" s="13">
+        <v>200</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" s="13">
-        <v>150</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="D12" s="14">
-        <v>130</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D13" s="14">
-        <v>200</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D14" s="14">
+      <c r="C15" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="13">
         <v>70</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="D15" s="15">
-        <v>120</v>
-      </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D17" s="13">
+        <v>69.8</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" s="13">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F18" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" s="11">
+        <v>2.25</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="11">
+        <v>2.75</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F20" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="15">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="15">
+        <v>17</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="15">
+        <v>12</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="15">
+        <v>17</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="15">
+        <v>12</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="15">
+        <v>25</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D31" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D33" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D34" s="15">
+        <v>3</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="D35" s="21">
+        <v>2</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D36" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D43" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E43" s="11"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="11">
+        <v>35.4</v>
+      </c>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="11">
+        <v>35.4</v>
+      </c>
+      <c r="E46" s="11"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="11">
+        <v>35.4</v>
+      </c>
+      <c r="E47" s="11"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" s="11">
+        <v>35.4</v>
+      </c>
+      <c r="E48" s="11"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E49" s="11"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E50" s="11"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D51" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E51" s="11"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D52" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E52" s="11"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D53" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E53" s="11"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D54" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E54" s="11"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E55" s="11"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E56" s="11"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D57" s="19">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D58" s="19">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" s="19">
+        <v>2018.3</v>
+      </c>
+      <c r="E59" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="D60" s="19">
+        <v>2022.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C61" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" s="14">
-        <v>69.8</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="F16" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="D17" s="14">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="E17" s="14" t="s">
+      <c r="D61" s="19">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D62" s="19">
+        <v>2015.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C63" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="F17" t="s">
+      <c r="D63" s="19">
+        <v>2024.3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="D64" s="19">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D18" s="12">
-        <v>2.25</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D19" s="12">
-        <v>2.75</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F19" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="D20" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F20" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D21" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F21" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D22" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" s="12">
-        <v>0.75</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D24" s="16">
-        <v>1</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D25" s="16">
-        <v>17</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" s="16">
-        <v>12</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="D27" s="16">
-        <v>17</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D28" s="16">
-        <v>12</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="D29" s="16">
-        <v>25</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D30" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="D31" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D32" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="D33" s="16">
-        <v>3</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="D34" s="17">
-        <v>2</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="D35" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="E35" s="12"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="E36" s="12"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D37" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="E37" s="12"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D38" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="E38" s="12"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D39" s="12">
-        <v>13.2</v>
-      </c>
-      <c r="E39" s="12"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D40" s="12">
-        <v>13.2</v>
-      </c>
-      <c r="E40" s="12"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D41" s="12">
-        <v>13.2</v>
-      </c>
-      <c r="E41" s="12"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="12">
-        <v>13.2</v>
-      </c>
-      <c r="E42" s="12"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="D43" s="12">
-        <v>35.4</v>
-      </c>
-      <c r="E43" s="12"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D44" s="12">
-        <v>35.4</v>
-      </c>
-      <c r="E44" s="12"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="12">
-        <v>35.4</v>
-      </c>
-      <c r="E45" s="12"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="12">
-        <v>35.4</v>
-      </c>
-      <c r="E46" s="12"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="D47" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="E47" s="12"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="D48" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="E48" s="12"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D49" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="E49" s="12"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D50" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="E50" s="12"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D51" s="12">
-        <v>11.4</v>
-      </c>
-      <c r="E51" s="12"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="D52" s="12">
-        <v>11.4</v>
-      </c>
-      <c r="E52" s="12"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D53" s="12">
-        <v>11.4</v>
-      </c>
-      <c r="E53" s="12"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D54" s="12">
-        <v>11.4</v>
-      </c>
-      <c r="E54" s="12"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="D55" s="20">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D56" s="20">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="D57" s="20">
-        <v>2018.3</v>
-      </c>
-      <c r="E57" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="D58" s="20">
-        <v>2022.15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="D59" s="20">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="D60" s="20">
-        <v>2015.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="D61" s="20">
-        <v>2024.3</v>
-      </c>
-      <c r="E61" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="D62" s="20">
+      <c r="C65" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D65" s="19">
         <v>2040</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="D63" s="20">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" t="s">
-        <v>120</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D64" s="21">
-        <v>100</v>
-      </c>
-      <c r="E64" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" t="s">
-        <v>120</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D65" s="21">
-        <v>100</v>
-      </c>
-      <c r="E65" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D66" s="21">
-        <v>100</v>
+      <c r="D66" s="7">
+        <v>0.27033795990919401</v>
       </c>
       <c r="E66" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -2982,16 +2931,16 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="8">
-        <v>0.27033795990919401</v>
+        <v>17</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="7">
+        <v>8.0685220845966698E-3</v>
       </c>
       <c r="E67" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -2999,16 +2948,16 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="8">
-        <v>8.0685220845966698E-3</v>
+        <v>16</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="7">
+        <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -3016,16 +2965,16 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="8">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69" s="7">
+        <v>0.04</v>
       </c>
       <c r="E69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -3033,16 +2982,13 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D70" s="8">
-        <v>3.7169338814298597E-2</v>
-      </c>
-      <c r="E70" t="s">
-        <v>129</v>
+        <v>222</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -3050,30 +2996,16 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>229</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D71" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s">
-        <v>233</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="D72" s="8">
+        <v>226</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="D71" s="7">
         <v>2000</v>
       </c>
-      <c r="E72" t="s">
-        <v>124</v>
+      <c r="E71" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E31A9C1-FA6D-4FA1-BCC3-1CF719654E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4FF692-8EFF-4483-B2B1-A21357A53527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="269">
   <si>
     <t>category</t>
   </si>
@@ -922,6 +922,33 @@
   </si>
   <si>
     <t>labour_cost_2005</t>
+  </si>
+  <si>
+    <t>space heating energy passive houses</t>
+  </si>
+  <si>
+    <t>q_passive</t>
+  </si>
+  <si>
+    <t>kWh/m2/y</t>
+  </si>
+  <si>
+    <t>domestic hot water heating</t>
+  </si>
+  <si>
+    <t>domestric lighting</t>
+  </si>
+  <si>
+    <t>q_lighting</t>
+  </si>
+  <si>
+    <t>space heating rebound</t>
+  </si>
+  <si>
+    <t>r.</t>
+  </si>
+  <si>
+    <t>q_hotwater</t>
   </si>
 </sst>
 </file>
@@ -1838,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -2462,74 +2489,80 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="D36" s="21">
+        <v>15</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D37" s="21">
+        <v>30</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D38" s="21">
+        <v>8</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C39" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D39" s="16">
         <v>0.75</v>
       </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D37" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E37" s="11"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D38" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E38" s="11"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E39" s="11"/>
+      <c r="E39" s="16"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>167</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D40" s="11">
         <v>11.8</v>
@@ -2541,13 +2574,13 @@
         <v>167</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D41" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" s="11"/>
     </row>
@@ -2556,13 +2589,13 @@
         <v>167</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D42" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" s="11"/>
     </row>
@@ -2571,13 +2604,13 @@
         <v>167</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D43" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" s="11"/>
     </row>
@@ -2589,7 +2622,7 @@
         <v>173</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D44" s="11">
         <v>13.2</v>
@@ -2601,29 +2634,28 @@
         <v>167</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D45" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>167</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D46" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E46" s="11"/>
     </row>
@@ -2632,13 +2664,13 @@
         <v>167</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D47" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E47" s="11"/>
     </row>
@@ -2650,25 +2682,26 @@
         <v>178</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D48" s="11">
         <v>35.4</v>
       </c>
       <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>167</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="D49" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E49" s="11"/>
     </row>
@@ -2677,13 +2710,13 @@
         <v>167</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="D50" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E50" s="11"/>
     </row>
@@ -2692,13 +2725,13 @@
         <v>167</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="D51" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E51" s="11"/>
     </row>
@@ -2710,7 +2743,7 @@
         <v>227</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D52" s="11">
         <v>0.4</v>
@@ -2722,13 +2755,13 @@
         <v>167</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="D53" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E53" s="11"/>
     </row>
@@ -2737,13 +2770,13 @@
         <v>167</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="D54" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E54" s="11"/>
     </row>
@@ -2752,25 +2785,25 @@
         <v>167</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="D55" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E55" s="11"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>183</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D56" s="11">
         <v>11.4</v>
@@ -2778,76 +2811,76 @@
       <c r="E56" s="11"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="D57" s="19">
-        <v>0.13500000000000001</v>
-      </c>
+      <c r="A57" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D57" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D58" s="19">
-        <v>0.23</v>
-      </c>
+      <c r="A58" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E58" s="11"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="D59" s="19">
-        <v>2018.3</v>
-      </c>
-      <c r="E59" t="s">
-        <v>208</v>
-      </c>
+      <c r="A59" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="19" t="s">
-        <v>206</v>
+      <c r="B60" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="D60" s="19">
-        <v>2022.15</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="19" t="s">
-        <v>224</v>
+      <c r="B61" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="D61" s="19">
-        <v>2011</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -2855,13 +2888,16 @@
         <v>6</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D62" s="19">
-        <v>2015.3</v>
+        <v>2018.3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -2869,16 +2905,13 @@
         <v>6</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D63" s="19">
-        <v>2024.3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>209</v>
+        <v>2022.15</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -2886,13 +2919,13 @@
         <v>6</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D64" s="19">
-        <v>2040</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -2900,64 +2933,58 @@
         <v>6</v>
       </c>
       <c r="B65" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D65" s="19">
+        <v>2015.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D66" s="19">
+        <v>2024.3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="D67" s="19">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C68" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D68" s="19">
         <v>2040</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" s="7">
-        <v>0.27033795990919401</v>
-      </c>
-      <c r="E66" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="7">
-        <v>8.0685220845966698E-3</v>
-      </c>
-      <c r="E67" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" s="7">
-        <v>0</v>
-      </c>
-      <c r="E68" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -2965,16 +2992,16 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D69" s="7">
-        <v>0.04</v>
+        <v>0.27033795990919401</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2982,13 +3009,16 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D70" s="7">
-        <v>0.8</v>
+        <v>8.0685220845966698E-3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2996,16 +3026,81 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="7">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D72" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="E72" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
         <v>226</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C74" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D74" s="7">
         <v>2000</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E74" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>266</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D75" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E75" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4FF692-8EFF-4483-B2B1-A21357A53527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B410D13-4209-4824-8DD1-C340A5015D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="282">
   <si>
     <t>category</t>
   </si>
@@ -516,9 +516,6 @@
     <t>not used, bias corrected at micro calibration stage</t>
   </si>
   <si>
-    <t>macro calibration: 3% may be consistent with RoI required by depositors</t>
-  </si>
-  <si>
     <t>scenario_BASE_1</t>
   </si>
   <si>
@@ -949,6 +946,48 @@
   </si>
   <si>
     <t>q_hotwater</t>
+  </si>
+  <si>
+    <t>ber_upgrade_marginal_cost_c0</t>
+  </si>
+  <si>
+    <t>low hanging fruit</t>
+  </si>
+  <si>
+    <t>inefficient house limit</t>
+  </si>
+  <si>
+    <t>rename to r.</t>
+  </si>
+  <si>
+    <t>present_bias_threshold</t>
+  </si>
+  <si>
+    <t>behaviour</t>
+  </si>
+  <si>
+    <t>present bias activation threshold</t>
+  </si>
+  <si>
+    <t>rebound activation threshold</t>
+  </si>
+  <si>
+    <t>rebound_threshold</t>
+  </si>
+  <si>
+    <t>no bias below this value but its probably heterogeneous</t>
+  </si>
+  <si>
+    <t>no rebound below this BER National Heat Study</t>
+  </si>
+  <si>
+    <t>labour cost share efficiency retrofit</t>
+  </si>
+  <si>
+    <t>guess</t>
+  </si>
+  <si>
+    <t>ber_upgrade_labour_cost_share</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1482,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1462,32 +1501,32 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="C5" s="2"/>
     </row>
@@ -1865,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -1898,135 +1937,135 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="D2" s="9">
         <v>2196</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" t="s">
         <v>139</v>
-      </c>
-      <c r="F2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" s="9">
         <v>16</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="C4" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D4" s="13">
         <v>30</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>135</v>
-      </c>
       <c r="C5" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="12">
         <v>40</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="C6" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="13">
         <v>60</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="C7" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="13">
         <v>60</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>135</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D8" s="14">
         <v>60</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D9" s="10">
         <v>700</v>
@@ -2037,13 +2076,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -2052,13 +2091,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2067,13 +2106,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D12" s="12">
         <v>150</v>
@@ -2084,13 +2123,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D13" s="13">
         <v>130</v>
@@ -2101,13 +2140,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D14" s="13">
         <v>200</v>
@@ -2118,13 +2157,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D15" s="13">
         <v>70</v>
@@ -2135,13 +2174,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D16" s="14">
         <v>120</v>
@@ -2152,79 +2191,82 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D17" s="13">
+        <v>110</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17" t="s">
         <v>218</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="D17" s="13">
-        <v>69.8</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="F17" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>216</v>
-      </c>
       <c r="D18" s="13">
-        <v>0.66700000000000004</v>
+        <v>0.81</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D19" s="11">
-        <v>2.25</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>203</v>
+      <c r="A19" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="D20" s="11">
-        <v>2.75</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F20" t="s">
-        <v>250</v>
+      <c r="A20" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2232,19 +2274,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D21" s="11">
-        <v>0.6</v>
+        <v>2.25</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F21" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2252,19 +2291,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D22" s="11">
-        <v>0.85</v>
+        <v>2.75</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2272,16 +2311,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>247</v>
-      </c>
       <c r="D23" s="11">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
+      </c>
+      <c r="F23" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2289,78 +2331,81 @@
         <v>18</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D24" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="11">
         <v>0.75</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="D25" s="15">
-        <v>1</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D26" s="15">
-        <v>17</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>9</v>
+      <c r="E26" s="11" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>153</v>
+        <v>255</v>
       </c>
       <c r="D27" s="15">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D28" s="15">
         <v>17</v>
@@ -2371,13 +2416,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D29" s="15">
         <v>12</v>
@@ -2388,16 +2433,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>192</v>
-      </c>
       <c r="D30" s="15">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E30" s="15" t="s">
         <v>9</v>
@@ -2405,432 +2450,436 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="D31" s="15">
-        <v>2.5</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>203</v>
+        <v>12</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B32" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="15">
+        <v>25</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D34" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D35" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="D32" s="15">
-        <v>2.5</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B33" s="15" t="s">
+      <c r="C36" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="D33" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" s="15">
+      <c r="D36" s="15">
         <v>3</v>
       </c>
-      <c r="E34" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="C35" s="21" t="s">
+      <c r="E36" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="D35" s="21">
+      <c r="C37" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D37" s="21">
         <v>2</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="D36" s="21">
-        <v>15</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="D37" s="21">
-        <v>30</v>
-      </c>
       <c r="E37" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B38" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="D38" s="21">
+        <v>15</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D39" s="21">
+        <v>30</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" s="21">
+      <c r="D40" s="21">
         <v>8</v>
       </c>
-      <c r="E38" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
+      <c r="E40" s="21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B41" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="D39" s="16">
+      <c r="D41" s="16">
         <v>0.75</v>
       </c>
-      <c r="E39" s="16"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E40" s="11"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" s="11" t="s">
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D41" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E41" s="11"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="D42" s="11">
         <v>11.8</v>
       </c>
       <c r="E42" s="11"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>168</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D43" s="11">
         <v>11.8</v>
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="C44" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="E45" s="11"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="D44" s="11">
-        <v>13.2</v>
-      </c>
-      <c r="E44" s="11"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D45" s="11">
-        <v>13.2</v>
-      </c>
-      <c r="E45" s="11"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="D46" s="11">
         <v>13.2</v>
       </c>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D47" s="11">
         <v>13.2</v>
       </c>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E48" s="11"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="E49" s="11"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D48" s="11">
-        <v>35.4</v>
-      </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="11">
-        <v>35.4</v>
-      </c>
-      <c r="E49" s="11"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="D50" s="11">
         <v>35.4</v>
       </c>
       <c r="E50" s="11"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D51" s="11">
         <v>35.4</v>
       </c>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="D52" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="D53" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D54" s="11">
         <v>0.4</v>
       </c>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D55" s="11">
         <v>0.4</v>
       </c>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="D56" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="D57" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>186</v>
@@ -2840,12 +2889,12 @@
       </c>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>184</v>
@@ -2855,252 +2904,325 @@
       </c>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="D60" s="19">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C61" s="18" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="19">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B60" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D60" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E60" s="11"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E61" s="11"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="19" t="s">
-        <v>205</v>
+      <c r="B62" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="D62" s="19">
-        <v>2018.3</v>
-      </c>
-      <c r="E62" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="19" t="s">
-        <v>206</v>
+      <c r="B63" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="D63" s="19">
-        <v>2022.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D64" s="19">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2018.3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="D65" s="19">
-        <v>2015.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2022.15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D66" s="19">
-        <v>2024.3</v>
-      </c>
-      <c r="E66" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D67" s="19">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2015.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D68" s="19">
+        <v>2024.3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D69" s="19">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C68" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="D68" s="19">
+      <c r="D70" s="19">
         <v>2040</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" t="s">
-        <v>15</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D69" s="7">
-        <v>0.27033795990919401</v>
-      </c>
-      <c r="E69" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="7">
-        <v>8.0685220845966698E-3</v>
-      </c>
-      <c r="E70" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" s="7">
-        <v>0</v>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D71" s="19">
+        <v>3000</v>
       </c>
       <c r="E71" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D72" s="7">
-        <v>0.04</v>
+        <v>119</v>
+      </c>
+      <c r="F71" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="D72" s="19">
+        <v>50</v>
       </c>
       <c r="E72" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+      <c r="F72" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>222</v>
-      </c>
-      <c r="C73" s="20" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D73" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.27033795990919401</v>
+      </c>
+      <c r="E73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>226</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>223</v>
+        <v>17</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D74" s="7">
-        <v>2000</v>
+        <v>8.0685220845966698E-3</v>
       </c>
       <c r="E74" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>11</v>
       </c>
       <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="7">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D76" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="E76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" t="s">
+        <v>221</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E77" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" t="s">
+        <v>225</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" s="7">
+        <v>2000</v>
+      </c>
+      <c r="E78" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" t="s">
+        <v>265</v>
+      </c>
+      <c r="C79" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="C75" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="D75" s="7">
+      <c r="D79" s="7">
         <v>0.5</v>
       </c>
-      <c r="E75" t="s">
-        <v>203</v>
+      <c r="E79" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B410D13-4209-4824-8DD1-C340A5015D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FE397A-4359-499C-BBD7-B5E6AF54F993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="287">
   <si>
     <t>category</t>
   </si>
@@ -988,6 +988,21 @@
   </si>
   <si>
     <t>ber_upgrade_labour_cost_share</t>
+  </si>
+  <si>
+    <t>Warmer Homes target BER</t>
+  </si>
+  <si>
+    <t>Warmer Homes heat pump preference</t>
+  </si>
+  <si>
+    <t>warmer_homes_target_ber</t>
+  </si>
+  <si>
+    <t>warmer_homes_heat_pump</t>
+  </si>
+  <si>
+    <t>decimal time</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1053,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1071,6 +1086,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -1111,15 +1132,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1152,12 +1174,16 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="6" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
     <cellStyle name="20% - Accent2" xfId="3" builtinId="34"/>
     <cellStyle name="20% - Accent3" xfId="4" builtinId="38"/>
     <cellStyle name="20% - Accent4" xfId="5" builtinId="42"/>
+    <cellStyle name="60% - Accent5" xfId="6" builtinId="48"/>
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1904,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -3012,13 +3038,16 @@
         <v>6</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="D67" s="19">
-        <v>2015.3</v>
+        <v>120</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3026,16 +3055,16 @@
         <v>6</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="D68" s="19">
-        <v>2024.3</v>
-      </c>
-      <c r="E68" t="s">
-        <v>208</v>
+        <v>2025</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3043,13 +3072,13 @@
         <v>6</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="D69" s="19">
-        <v>2040</v>
+        <v>2015.3</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -3057,87 +3086,84 @@
         <v>6</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D70" s="19">
-        <v>2040</v>
+        <v>2024.3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
-        <v>273</v>
+        <v>6</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>272</v>
+        <v>213</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>211</v>
       </c>
       <c r="D71" s="19">
-        <v>3000</v>
-      </c>
-      <c r="E71" t="s">
-        <v>119</v>
-      </c>
-      <c r="F71" t="s">
-        <v>277</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D72" s="19">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B73" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" s="24">
+        <v>3000</v>
+      </c>
+      <c r="E73" t="s">
+        <v>119</v>
+      </c>
+      <c r="F73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="B74" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C74" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="D72" s="19">
+      <c r="D74" s="24">
         <v>50</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E74" t="s">
         <v>261</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F74" t="s">
         <v>278</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>11</v>
-      </c>
-      <c r="B73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" s="7">
-        <v>0.27033795990919401</v>
-      </c>
-      <c r="E73" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>11</v>
-      </c>
-      <c r="B74" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="7">
-        <v>8.0685220845966698E-3</v>
-      </c>
-      <c r="E74" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3145,16 +3171,16 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D75" s="7">
-        <v>0</v>
+        <v>0.27033795990919401</v>
       </c>
       <c r="E75" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3162,16 +3188,16 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="D76" s="7">
-        <v>0.04</v>
+        <v>8.0685220845966698E-3</v>
       </c>
       <c r="E76" t="s">
-        <v>271</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3179,16 +3205,16 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>221</v>
-      </c>
-      <c r="C77" s="20" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="D77" s="7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3196,16 +3222,16 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>225</v>
-      </c>
-      <c r="C78" s="20" t="s">
-        <v>222</v>
+        <v>10</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="D78" s="7">
-        <v>2000</v>
+        <v>0.04</v>
       </c>
       <c r="E78" t="s">
-        <v>119</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3213,16 +3239,53 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>266</v>
+        <v>12</v>
       </c>
       <c r="D79" s="7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E79" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D80" s="7">
+        <v>2000</v>
+      </c>
+      <c r="E80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" t="s">
+        <v>265</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D81" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E81" t="s">
+        <v>202</v>
+      </c>
+      <c r="F81" s="22">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FE397A-4359-499C-BBD7-B5E6AF54F993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AEE79D-4B3F-4216-BC06-F1F2D6E570C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="288">
   <si>
     <t>category</t>
   </si>
@@ -507,9 +507,6 @@
     <t>nu.</t>
   </si>
   <si>
-    <t>delta.</t>
-  </si>
-  <si>
     <t>macro calibration</t>
   </si>
   <si>
@@ -810,9 +807,6 @@
     <t>present bias beta</t>
   </si>
   <si>
-    <t>h.</t>
-  </si>
-  <si>
     <t>Warmer Homes scheme (current)</t>
   </si>
   <si>
@@ -1003,6 +997,15 @@
   </si>
   <si>
     <t>decimal time</t>
+  </si>
+  <si>
+    <t>rho.</t>
+  </si>
+  <si>
+    <t>eta.</t>
+  </si>
+  <si>
+    <t>for OSS the effective present bias is beta*eta.</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1511,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1527,32 +1530,32 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="C5" s="2"/>
     </row>
@@ -1963,135 +1966,135 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="D2" s="9">
         <v>2196</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" t="s">
         <v>138</v>
-      </c>
-      <c r="F2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" s="9">
         <v>16</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="C4" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D4" s="13">
         <v>30</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>134</v>
-      </c>
       <c r="C5" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="12">
         <v>40</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="C6" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D6" s="13">
         <v>60</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="C7" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7" s="13">
         <v>60</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>134</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D8" s="14">
         <v>60</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D9" s="10">
         <v>700</v>
@@ -2102,13 +2105,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -2117,13 +2120,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2132,13 +2135,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="12">
         <v>150</v>
@@ -2149,13 +2152,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D13" s="13">
         <v>130</v>
@@ -2166,13 +2169,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D14" s="13">
         <v>200</v>
@@ -2183,13 +2186,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D15" s="13">
         <v>70</v>
@@ -2200,13 +2203,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D16" s="14">
         <v>120</v>
@@ -2217,53 +2220,53 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D17" s="13">
         <v>110</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="D18" s="13">
         <v>0.81</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -2272,27 +2275,27 @@
         <v>119</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B20" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>281</v>
       </c>
       <c r="D20" s="13">
         <v>0.3</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2300,16 +2303,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D21" s="11">
         <v>2.25</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2317,19 +2320,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D22" s="11">
         <v>2.75</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2337,19 +2340,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D23" s="11">
         <v>0.6</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2357,19 +2360,19 @@
         <v>18</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>243</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="D24" s="11">
         <v>0.85</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F24" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2377,16 +2380,16 @@
         <v>18</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D25" s="11">
         <v>0.9</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2394,16 +2397,16 @@
         <v>18</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D26" s="11">
         <v>0.75</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2411,27 +2414,27 @@
         <v>18</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>149</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>150</v>
       </c>
       <c r="D28" s="15">
         <v>17</v>
@@ -2442,13 +2445,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>151</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>152</v>
       </c>
       <c r="D29" s="15">
         <v>12</v>
@@ -2459,13 +2462,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>160</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>161</v>
       </c>
       <c r="D30" s="15">
         <v>17</v>
@@ -2476,13 +2479,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D31" s="15">
         <v>12</v>
@@ -2493,13 +2496,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D32" s="15">
         <v>25</v>
@@ -2510,87 +2513,87 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D33" s="15">
         <v>2.5</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D34" s="15">
         <v>2.5</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D35" s="15">
         <v>1.5</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B36" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>240</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>242</v>
       </c>
       <c r="D36" s="15">
         <v>3</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D37" s="21">
         <v>2</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2598,16 +2601,16 @@
         <v>18</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D38" s="21">
         <v>15</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2615,16 +2618,16 @@
         <v>18</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D39" s="21">
         <v>30</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2632,16 +2635,16 @@
         <v>18</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D40" s="21">
         <v>8</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2649,10 +2652,10 @@
         <v>18</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D41" s="16">
         <v>0.75</v>
@@ -2661,13 +2664,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D42" s="11">
         <v>11.8</v>
@@ -2676,13 +2679,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>167</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D43" s="11">
         <v>11.8</v>
@@ -2691,13 +2694,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>167</v>
-      </c>
       <c r="C44" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D44" s="11">
         <v>11.8</v>
@@ -2706,13 +2709,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>167</v>
-      </c>
       <c r="C45" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D45" s="11">
         <v>11.8</v>
@@ -2721,13 +2724,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B46" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="D46" s="11">
         <v>13.2</v>
@@ -2736,13 +2739,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D47" s="11">
         <v>13.2</v>
@@ -2751,13 +2754,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D48" s="11">
         <v>13.2</v>
@@ -2766,13 +2769,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D49" s="11">
         <v>13.2</v>
@@ -2781,13 +2784,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B50" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="D50" s="11">
         <v>35.4</v>
@@ -2797,13 +2800,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D51" s="11">
         <v>35.4</v>
@@ -2812,13 +2815,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D52" s="11">
         <v>35.4</v>
@@ -2827,13 +2830,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D53" s="11">
         <v>35.4</v>
@@ -2842,13 +2845,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D54" s="11">
         <v>0.4</v>
@@ -2857,13 +2860,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D55" s="11">
         <v>0.4</v>
@@ -2872,13 +2875,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D56" s="11">
         <v>0.4</v>
@@ -2887,13 +2890,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D57" s="11">
         <v>0.4</v>
@@ -2902,13 +2905,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D58" s="11">
         <v>11.4</v>
@@ -2917,13 +2920,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D59" s="11">
         <v>11.4</v>
@@ -2932,13 +2935,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D60" s="11">
         <v>11.4</v>
@@ -2950,10 +2953,10 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="D61" s="11">
         <v>11.4</v>
@@ -2965,10 +2968,10 @@
         <v>6</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D62" s="19">
         <v>0.13500000000000001</v>
@@ -2979,10 +2982,10 @@
         <v>6</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D63" s="19">
         <v>0.23</v>
@@ -2993,16 +2996,16 @@
         <v>6</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D64" s="19">
         <v>2018.3</v>
       </c>
       <c r="E64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -3010,10 +3013,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D65" s="19">
         <v>2022.15</v>
@@ -3024,10 +3027,10 @@
         <v>6</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D66" s="19">
         <v>2011</v>
@@ -3038,16 +3041,16 @@
         <v>6</v>
       </c>
       <c r="B67" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C67" s="18" t="s">
         <v>282</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>284</v>
       </c>
       <c r="D67" s="19">
         <v>120</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3055,16 +3058,16 @@
         <v>6</v>
       </c>
       <c r="B68" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C68" s="18" t="s">
         <v>283</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>285</v>
       </c>
       <c r="D68" s="19">
         <v>2025</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3072,10 +3075,10 @@
         <v>6</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D69" s="19">
         <v>2015.3</v>
@@ -3086,16 +3089,16 @@
         <v>6</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D70" s="19">
         <v>2024.3</v>
       </c>
       <c r="E70" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3103,10 +3106,10 @@
         <v>6</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D71" s="19">
         <v>2040</v>
@@ -3117,10 +3120,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D72" s="19">
         <v>2040</v>
@@ -3128,13 +3131,13 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D73" s="24">
         <v>3000</v>
@@ -3143,27 +3146,27 @@
         <v>119</v>
       </c>
       <c r="F73" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="B74" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="B74" s="24" t="s">
-        <v>275</v>
-      </c>
       <c r="C74" s="24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D74" s="24">
         <v>50</v>
       </c>
       <c r="E74" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F74" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3180,7 +3183,7 @@
         <v>0.27033795990919401</v>
       </c>
       <c r="E75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3197,7 +3200,7 @@
         <v>8.0685220845966698E-3</v>
       </c>
       <c r="E76" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3214,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3225,13 +3228,13 @@
         <v>10</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>121</v>
+        <v>264</v>
       </c>
       <c r="D78" s="7">
         <v>0.04</v>
       </c>
       <c r="E78" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3239,7 +3242,7 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>12</v>
@@ -3248,7 +3251,7 @@
         <v>0.8</v>
       </c>
       <c r="E79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3256,16 +3259,16 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="D80" s="7">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="E80" t="s">
-        <v>119</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3273,16 +3276,16 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="D81" s="7">
         <v>0.3</v>
       </c>
       <c r="E81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F81" s="22">
         <v>0.3</v>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AEE79D-4B3F-4216-BC06-F1F2D6E570C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90197CF-AE51-4833-8BA9-7512E9C5CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="252" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="300">
   <si>
     <t>category</t>
   </si>
@@ -915,9 +915,6 @@
     <t>labour_cost_2005</t>
   </si>
   <si>
-    <t>space heating energy passive houses</t>
-  </si>
-  <si>
     <t>q_passive</t>
   </si>
   <si>
@@ -1006,6 +1003,45 @@
   </si>
   <si>
     <t>for OSS the effective present bias is beta*eta.</t>
+  </si>
+  <si>
+    <t>HLI threshold for heat pump support</t>
+  </si>
+  <si>
+    <t>space heating primary energy passive houses</t>
+  </si>
+  <si>
+    <t>hli_heat_pump_threshold</t>
+  </si>
+  <si>
+    <t>W/Km2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEAI </t>
+  </si>
+  <si>
+    <t>pef for electricity 2030</t>
+  </si>
+  <si>
+    <t>pef for electricity 2040</t>
+  </si>
+  <si>
+    <t>pef for electricity 2050</t>
+  </si>
+  <si>
+    <t>pef_electricity_2030</t>
+  </si>
+  <si>
+    <t>pef_electricity_2040</t>
+  </si>
+  <si>
+    <t>pef_electricity_2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLI upgrade social effect </t>
+  </si>
+  <si>
+    <t>sigma.</t>
   </si>
 </sst>
 </file>
@@ -1933,11 +1969,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.88671875" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="10.5546875" customWidth="1"/>
@@ -2263,10 +2299,10 @@
         <v>132</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -2275,7 +2311,7 @@
         <v>119</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2283,10 +2319,10 @@
         <v>132</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D20" s="13">
         <v>0.3</v>
@@ -2295,7 +2331,7 @@
         <v>201</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2511,7 +2547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>159</v>
       </c>
@@ -2528,7 +2564,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>159</v>
       </c>
@@ -2545,7 +2581,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>159</v>
       </c>
@@ -2562,7 +2598,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>159</v>
       </c>
@@ -2579,7 +2615,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>159</v>
       </c>
@@ -2596,174 +2632,181 @@
         <v>201</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B38" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>257</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>258</v>
       </c>
       <c r="D38" s="21">
         <v>15</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D39" s="21">
         <v>30</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B40" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>261</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>262</v>
       </c>
       <c r="D40" s="21">
         <v>8</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D41" s="21">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="F41" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D42" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="E42" s="21"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" s="21">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E43" s="21"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D44" s="21">
+        <v>1.08</v>
+      </c>
+      <c r="E44" s="21"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D41" s="16">
-        <v>0.75</v>
-      </c>
-      <c r="E41" s="16"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D42" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E42" s="11"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E43" s="11"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E44" s="11"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D45" s="11">
-        <v>11.8</v>
-      </c>
-      <c r="E45" s="11"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D45" s="16">
+        <v>0</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D46" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D47" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D48" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" s="11"/>
     </row>
@@ -2772,13 +2815,13 @@
         <v>165</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D49" s="11">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" s="11"/>
     </row>
@@ -2787,29 +2830,28 @@
         <v>165</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D50" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D51" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E51" s="11"/>
     </row>
@@ -2818,13 +2860,13 @@
         <v>165</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D52" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E52" s="11"/>
     </row>
@@ -2833,13 +2875,13 @@
         <v>165</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D53" s="11">
-        <v>35.4</v>
+        <v>13.2</v>
       </c>
       <c r="E53" s="11"/>
     </row>
@@ -2848,28 +2890,29 @@
         <v>165</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="D54" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>165</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="D55" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E55" s="11"/>
     </row>
@@ -2878,13 +2921,13 @@
         <v>165</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="D56" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E56" s="11"/>
     </row>
@@ -2893,13 +2936,13 @@
         <v>165</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="D57" s="11">
-        <v>0.4</v>
+        <v>35.4</v>
       </c>
       <c r="E57" s="11"/>
     </row>
@@ -2908,13 +2951,13 @@
         <v>165</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="D58" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E58" s="11"/>
     </row>
@@ -2923,13 +2966,13 @@
         <v>165</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="D59" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E59" s="11"/>
     </row>
@@ -2938,119 +2981,117 @@
         <v>165</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="D60" s="11">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E60" s="11"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E61" s="11"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E62" s="11"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E63" s="11"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="E64" s="11"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B65" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C65" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D65" s="11">
         <v>11.4</v>
       </c>
-      <c r="E61" s="11"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="D62" s="19">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D63" s="19">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D64" s="19">
-        <v>2018.3</v>
-      </c>
-      <c r="E64" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="D65" s="19">
-        <v>2022.15</v>
-      </c>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B66" s="19" t="s">
-        <v>221</v>
+      <c r="B66" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="D66" s="19">
-        <v>2011</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="19" t="s">
-        <v>280</v>
+      <c r="B67" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>282</v>
+        <v>164</v>
       </c>
       <c r="D67" s="19">
-        <v>120</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>259</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3058,16 +3099,16 @@
         <v>6</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>283</v>
+        <v>209</v>
       </c>
       <c r="D68" s="19">
-        <v>2025</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>284</v>
+        <v>2018.3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3075,13 +3116,13 @@
         <v>6</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="D69" s="19">
-        <v>2015.3</v>
+        <v>2022.15</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -3089,16 +3130,13 @@
         <v>6</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D70" s="19">
-        <v>2024.3</v>
-      </c>
-      <c r="E70" t="s">
-        <v>207</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3106,13 +3144,16 @@
         <v>6</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="D71" s="19">
-        <v>2040</v>
+        <v>120</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3120,121 +3161,115 @@
         <v>6</v>
       </c>
       <c r="B72" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D72" s="19">
+        <v>2025</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D73" s="19">
+        <v>2015.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74" s="19">
+        <v>2024.3</v>
+      </c>
+      <c r="E74" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D75" s="19">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="C72" s="18" t="s">
+      <c r="C76" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="D72" s="19">
+      <c r="D76" s="19">
         <v>2040</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="23" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B77" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="B73" s="24" t="s">
+      <c r="C77" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D77" s="24">
+        <v>3000</v>
+      </c>
+      <c r="E77" t="s">
+        <v>119</v>
+      </c>
+      <c r="F77" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B78" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="C73" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="D73" s="24">
-        <v>3000</v>
-      </c>
-      <c r="E73" t="s">
-        <v>119</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="C78" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D78" s="24">
+        <v>50</v>
+      </c>
+      <c r="E78" t="s">
+        <v>258</v>
+      </c>
+      <c r="F78" t="s">
         <v>275</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="D74" s="24">
-        <v>50</v>
-      </c>
-      <c r="E74" t="s">
-        <v>259</v>
-      </c>
-      <c r="F74" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>11</v>
-      </c>
-      <c r="B75" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D75" s="7">
-        <v>0.27033795990919401</v>
-      </c>
-      <c r="E75" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>11</v>
-      </c>
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="7">
-        <v>8.0685220845966698E-3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>11</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" s="7">
-        <v>0</v>
-      </c>
-      <c r="E77" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="D78" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="E78" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3242,16 +3277,16 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>220</v>
-      </c>
-      <c r="C79" s="20" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="D79" s="7">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="E79" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3259,16 +3294,16 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
-      </c>
-      <c r="C80" s="20" t="s">
-        <v>286</v>
+        <v>17</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D80" s="7">
-        <v>0.8</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="E80" t="s">
-        <v>287</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3276,19 +3311,104 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="7">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="C81" s="20" t="s">
+      <c r="D82" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="E82" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" t="s">
+        <v>220</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E83" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D84" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="E84" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" t="s">
+        <v>262</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="D85" s="7">
         <v>0.3</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E85" t="s">
         <v>201</v>
       </c>
-      <c r="F81" s="22">
+      <c r="F85" s="22">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s">
+        <v>298</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="D86" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90197CF-AE51-4833-8BA9-7512E9C5CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951385C3-CE04-4B1F-9D61-06FB59178B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="252" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="304">
   <si>
     <t>category</t>
   </si>
@@ -1042,6 +1042,18 @@
   </si>
   <si>
     <t>sigma.</t>
+  </si>
+  <si>
+    <t>warmer homes economy of scale factor</t>
+  </si>
+  <si>
+    <t>assume 20% discount to private market</t>
+  </si>
+  <si>
+    <t>warmer_homes_cost_scale</t>
+  </si>
+  <si>
+    <t>B3  in practice</t>
   </si>
 </sst>
 </file>
@@ -1969,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -3150,10 +3162,13 @@
         <v>281</v>
       </c>
       <c r="D71" s="19">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>258</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3233,23 +3248,20 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="B77" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="C77" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="D77" s="24">
-        <v>3000</v>
+      <c r="A77" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="D77" s="19">
+        <v>0.8</v>
       </c>
       <c r="E77" t="s">
-        <v>119</v>
-      </c>
-      <c r="F77" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3257,36 +3269,39 @@
         <v>270</v>
       </c>
       <c r="B78" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D78" s="24">
+        <v>3000</v>
+      </c>
+      <c r="E78" t="s">
+        <v>119</v>
+      </c>
+      <c r="F78" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B79" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C79" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="D78" s="24">
+      <c r="D79" s="24">
         <v>50</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E79" t="s">
         <v>258</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F79" t="s">
         <v>275</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>11</v>
-      </c>
-      <c r="B79" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="E79" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3294,13 +3309,13 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="D80" s="7">
-        <v>2.2000000000000001E-3</v>
+        <v>0.15</v>
       </c>
       <c r="E80" t="s">
         <v>121</v>
@@ -3311,16 +3326,16 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D81" s="7">
-        <v>0</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="E81" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3328,16 +3343,16 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>263</v>
+        <v>14</v>
       </c>
       <c r="D82" s="7">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>268</v>
+        <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3345,16 +3360,16 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>220</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>263</v>
       </c>
       <c r="D83" s="7">
-        <v>0.8</v>
+        <v>0.04</v>
       </c>
       <c r="E83" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3362,16 +3377,16 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>285</v>
+        <v>12</v>
       </c>
       <c r="D84" s="7">
         <v>0.8</v>
       </c>
       <c r="E84" t="s">
-        <v>286</v>
+        <v>201</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3379,19 +3394,16 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D85" s="7">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E85" t="s">
-        <v>201</v>
-      </c>
-      <c r="F85" s="22">
-        <v>0.3</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3399,15 +3411,35 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
+        <v>262</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="D86" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="E86" t="s">
+        <v>201</v>
+      </c>
+      <c r="F86" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" t="s">
         <v>298</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C87" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D87" s="7">
         <v>0.1</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E87" t="s">
         <v>201</v>
       </c>
     </row>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECBCE7E-9A0B-49B6-8797-FE5FD4A4A5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE784C7-D01A-46BE-8506-146056EFB7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="239">
   <si>
     <t>category</t>
   </si>
@@ -751,6 +751,12 @@
   </si>
   <si>
     <t>€/tCO2</t>
+  </si>
+  <si>
+    <t>minimum fabric grant amount</t>
+  </si>
+  <si>
+    <t>minimum_fabric_grant</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -2477,13 +2483,16 @@
         <v>6</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="D67" s="14">
-        <v>0.13500000000000001</v>
+        <v>700</v>
+      </c>
+      <c r="E67" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2491,30 +2500,27 @@
         <v>6</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" s="14">
-        <v>0.23</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B69" s="14" t="s">
-        <v>100</v>
+      <c r="B69" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="D69" s="14">
-        <v>2018.3</v>
-      </c>
-      <c r="E69" t="s">
-        <v>103</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2522,13 +2528,16 @@
         <v>6</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D70" s="14">
-        <v>2022.15</v>
+        <v>2018.3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2536,13 +2545,13 @@
         <v>6</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D71" s="14">
-        <v>2011</v>
+        <v>2022.15</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2550,19 +2559,13 @@
         <v>6</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="D72" s="14">
-        <v>150</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>200</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2570,16 +2573,19 @@
         <v>6</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D73" s="14">
-        <v>2025</v>
+        <v>150</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>180</v>
+        <v>155</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2587,13 +2593,16 @@
         <v>6</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="D74" s="14">
-        <v>2015.3</v>
+        <v>2025</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2601,16 +2610,13 @@
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D75" s="14">
-        <v>2024.3</v>
-      </c>
-      <c r="E75" t="s">
-        <v>104</v>
+        <v>2015.3</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2618,13 +2624,16 @@
         <v>6</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D76" s="14">
-        <v>2040</v>
+        <v>2024.3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2632,10 +2641,10 @@
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D77" s="14">
         <v>2040</v>
@@ -2646,16 +2655,13 @@
         <v>6</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>199</v>
+        <v>122</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="D78" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E78" t="s">
-        <v>198</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2663,16 +2669,16 @@
         <v>6</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="D79" s="14">
-        <v>63.5</v>
+        <v>0.8</v>
       </c>
       <c r="E79" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2680,13 +2686,13 @@
         <v>6</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D80" s="14">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="E80" t="s">
         <v>236</v>
@@ -2697,36 +2703,33 @@
         <v>6</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D81" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E81" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D82" s="19">
-        <v>3000</v>
+      <c r="A82" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D82" s="14">
+        <v>200</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
-      </c>
-      <c r="F82" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2734,36 +2737,39 @@
         <v>167</v>
       </c>
       <c r="B83" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="19">
+        <v>3000</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C84" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D83" s="19">
+      <c r="D84" s="19">
         <v>50</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E84" t="s">
         <v>155</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F84" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>11</v>
-      </c>
-      <c r="B84" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E84" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2771,13 +2777,13 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D85" s="3">
-        <v>2.2000000000000001E-3</v>
+        <v>0.15</v>
       </c>
       <c r="E85" t="s">
         <v>25</v>
@@ -2788,16 +2794,16 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D86" s="3">
-        <v>0</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="E86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2805,16 +2811,16 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
       <c r="D87" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2822,16 +2828,16 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="D88" s="3">
-        <v>0.8</v>
+        <v>0.04</v>
       </c>
       <c r="E88" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2839,19 +2845,16 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="D89" s="3">
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="E89" t="s">
         <v>98</v>
-      </c>
-      <c r="F89" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2859,19 +2862,19 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D90" s="3">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="E90" t="s">
         <v>98</v>
       </c>
-      <c r="F90" s="17">
-        <v>0.3</v>
+      <c r="F90" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2879,16 +2882,19 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E91" t="s">
         <v>98</v>
+      </c>
+      <c r="F91" s="17">
+        <v>0.3</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2896,18 +2902,35 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D92" s="3">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E92" t="s">
         <v>98</v>
       </c>
-      <c r="F92" t="s">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" t="s">
+        <v>213</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D93" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="E93" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" t="s">
         <v>212</v>
       </c>
     </row>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE784C7-D01A-46BE-8506-146056EFB7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9D47C9-9C63-4883-A578-DEFA75CD93FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="242">
   <si>
     <t>category</t>
   </si>
@@ -757,6 +757,15 @@
   </si>
   <si>
     <t>minimum_fabric_grant</t>
+  </si>
+  <si>
+    <t>Warmer Homes cost cap</t>
+  </si>
+  <si>
+    <t>lag effect (2 years)</t>
+  </si>
+  <si>
+    <t>warmer_homes_cost_cap</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -2593,30 +2602,37 @@
         <v>6</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="D74" s="14">
-        <v>2025</v>
+        <v>35000</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>180</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F74" s="14"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="D75" s="14">
-        <v>2015.3</v>
+        <v>2027</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2624,16 +2640,13 @@
         <v>6</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D76" s="14">
-        <v>2024.3</v>
-      </c>
-      <c r="E76" t="s">
-        <v>104</v>
+        <v>2015.3</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2641,13 +2654,16 @@
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D77" s="14">
-        <v>2040</v>
+        <v>2024.3</v>
+      </c>
+      <c r="E77" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2655,10 +2671,10 @@
         <v>6</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D78" s="14">
         <v>2040</v>
@@ -2669,16 +2685,13 @@
         <v>6</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>199</v>
+        <v>122</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="D79" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E79" t="s">
-        <v>198</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2686,16 +2699,16 @@
         <v>6</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="D80" s="14">
-        <v>63.5</v>
+        <v>0.8</v>
       </c>
       <c r="E80" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2703,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D81" s="14">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="E81" t="s">
         <v>236</v>
@@ -2720,36 +2733,33 @@
         <v>6</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D82" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" s="19">
-        <v>3000</v>
+      <c r="A83" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D83" s="14">
+        <v>200</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2757,36 +2767,39 @@
         <v>167</v>
       </c>
       <c r="B84" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" s="19">
+        <v>3000</v>
+      </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C85" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D84" s="19">
+      <c r="D85" s="19">
         <v>50</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E85" t="s">
         <v>155</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F85" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B85" t="s">
-        <v>15</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E85" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -2794,13 +2807,13 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D86" s="3">
-        <v>2.2000000000000001E-3</v>
+        <v>0.15</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
@@ -2811,16 +2824,16 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87" s="3">
-        <v>0</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2828,16 +2841,16 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
       <c r="D88" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2845,16 +2858,16 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>117</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="D89" s="3">
-        <v>0.8</v>
+        <v>0.04</v>
       </c>
       <c r="E89" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2862,19 +2875,16 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="D90" s="3">
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="E90" t="s">
         <v>98</v>
-      </c>
-      <c r="F90" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2882,19 +2892,19 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D91" s="3">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="E91" t="s">
         <v>98</v>
       </c>
-      <c r="F91" s="17">
-        <v>0.3</v>
+      <c r="F91" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2902,16 +2912,19 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D92" s="3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E92" t="s">
         <v>98</v>
+      </c>
+      <c r="F92" s="17">
+        <v>0.3</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2919,18 +2932,35 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D93" s="3">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E93" t="s">
         <v>98</v>
       </c>
-      <c r="F93" t="s">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" t="s">
+        <v>213</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D94" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="E94" t="s">
+        <v>98</v>
+      </c>
+      <c r="F94" t="s">
         <v>212</v>
       </c>
     </row>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9D47C9-9C63-4883-A578-DEFA75CD93FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A989D643-F66B-42CD-9CF4-80E46D8709F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="246">
   <si>
     <t>category</t>
   </si>
@@ -766,6 +766,18 @@
   </si>
   <si>
     <t>warmer_homes_cost_cap</t>
+  </si>
+  <si>
+    <t>nighr rate usage heat pumps</t>
+  </si>
+  <si>
+    <t>hp_night_rate_usage_factor</t>
+  </si>
+  <si>
+    <t>electric_night_rate_usage_factor</t>
+  </si>
+  <si>
+    <t>cost reduction</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -2134,37 +2146,43 @@
       <c r="E45" s="16"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" s="16">
+        <v>0</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D46" s="11">
-        <v>0</v>
-      </c>
-      <c r="E46" s="11" t="s">
+      <c r="C47" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D47" s="6">
-        <v>11.8</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>201</v>
+      <c r="F47" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2172,19 +2190,16 @@
         <v>62</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D48" s="6">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2195,13 +2210,16 @@
         <v>63</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D49" s="6">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>201</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2212,10 +2230,10 @@
         <v>63</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D50" s="6">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>201</v>
@@ -2226,13 +2244,13 @@
         <v>62</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D51" s="6">
-        <v>13.2</v>
+        <v>16.8</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>201</v>
@@ -2246,16 +2264,13 @@
         <v>68</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D52" s="6">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2266,13 +2281,16 @@
         <v>68</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D53" s="6">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>201</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2283,10 +2301,10 @@
         <v>68</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D54" s="6">
-        <v>17.2</v>
+        <v>14.8</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -2297,18 +2315,17 @@
         <v>62</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D55" s="6">
-        <v>35.4</v>
+        <v>17.2</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="6"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
@@ -2318,7 +2335,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D56" s="6">
         <v>35.4</v>
@@ -2326,6 +2343,7 @@
       <c r="E56" s="6" t="s">
         <v>201</v>
       </c>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
@@ -2335,7 +2353,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D57" s="6">
         <v>35.4</v>
@@ -2352,7 +2370,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D58" s="6">
         <v>35.4</v>
@@ -2366,15 +2384,17 @@
         <v>62</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="D59" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E59" s="6"/>
+        <v>35.4</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
@@ -2384,7 +2404,7 @@
         <v>121</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D60" s="6">
         <v>0.4</v>
@@ -2399,7 +2419,7 @@
         <v>121</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D61" s="6">
         <v>0.4</v>
@@ -2414,7 +2434,7 @@
         <v>121</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D62" s="6">
         <v>0.4</v>
@@ -2426,18 +2446,15 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D63" s="6">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E63" s="6"/>
-      <c r="F63" s="6" t="s">
-        <v>204</v>
-      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
@@ -2447,14 +2464,14 @@
         <v>78</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D64" s="6">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2465,57 +2482,61 @@
         <v>78</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D65" s="6">
-        <v>14</v>
+        <v>12.7</v>
       </c>
       <c r="E65" s="6"/>
+      <c r="F65" s="6" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="6">
+        <v>14</v>
+      </c>
+      <c r="E66" s="6"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D67" s="6">
         <v>17.899999999999999</v>
       </c>
-      <c r="E66" s="6"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="D67" s="14">
-        <v>700</v>
-      </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
+      <c r="E67" s="6"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="D68" s="14">
-        <v>0.13500000000000001</v>
+        <v>700</v>
+      </c>
+      <c r="E68" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2523,30 +2544,27 @@
         <v>6</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D69" s="14">
-        <v>0.23</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B70" s="14" t="s">
-        <v>100</v>
+      <c r="B70" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="D70" s="14">
-        <v>2018.3</v>
-      </c>
-      <c r="E70" t="s">
-        <v>103</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2554,13 +2572,16 @@
         <v>6</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D71" s="14">
-        <v>2022.15</v>
+        <v>2018.3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -2568,13 +2589,13 @@
         <v>6</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D72" s="14">
-        <v>2011</v>
+        <v>2022.15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2582,19 +2603,13 @@
         <v>6</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="D73" s="14">
-        <v>150</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F73" s="14" t="s">
-        <v>200</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2602,51 +2617,57 @@
         <v>6</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>241</v>
+        <v>178</v>
       </c>
       <c r="D74" s="14">
-        <v>35000</v>
+        <v>150</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F74" s="14"/>
+        <v>155</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="D75" s="14">
-        <v>2027</v>
+        <v>35000</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>240</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F75" s="14"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="D76" s="14">
-        <v>2015.3</v>
+        <v>2027</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2654,16 +2675,13 @@
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D77" s="14">
-        <v>2024.3</v>
-      </c>
-      <c r="E77" t="s">
-        <v>104</v>
+        <v>2015.3</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2671,13 +2689,16 @@
         <v>6</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D78" s="14">
-        <v>2040</v>
+        <v>2024.3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2685,10 +2706,10 @@
         <v>6</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D79" s="14">
         <v>2040</v>
@@ -2699,16 +2720,13 @@
         <v>6</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>199</v>
+        <v>122</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="D80" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E80" t="s">
-        <v>198</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2716,16 +2734,16 @@
         <v>6</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="D81" s="14">
-        <v>63.5</v>
+        <v>0.8</v>
       </c>
       <c r="E81" t="s">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2733,13 +2751,13 @@
         <v>6</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D82" s="14">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="E82" t="s">
         <v>236</v>
@@ -2750,36 +2768,33 @@
         <v>6</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D83" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C84" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D84" s="19">
-        <v>3000</v>
+      <c r="A84" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" s="14">
+        <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2787,36 +2802,39 @@
         <v>167</v>
       </c>
       <c r="B85" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D85" s="19">
+        <v>3000</v>
+      </c>
+      <c r="E85" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C86" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D85" s="19">
+      <c r="D86" s="19">
         <v>50</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E86" t="s">
         <v>155</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F86" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B86" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D86" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E86" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2824,13 +2842,13 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="3">
-        <v>2.2000000000000001E-3</v>
+        <v>24</v>
+      </c>
+      <c r="D87">
+        <v>0.710843770010396</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -2841,16 +2859,16 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" s="3">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="D88">
+        <v>1.14974246520316E-2</v>
       </c>
       <c r="E88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2858,16 +2876,16 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
       <c r="D89" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2875,16 +2893,16 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>117</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D90" s="3">
-        <v>0.8</v>
+        <v>10</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90">
+        <v>1.1404764768900301E-2</v>
       </c>
       <c r="E90" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2892,19 +2910,16 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="D91" s="3">
-        <v>0.02</v>
+        <v>12</v>
+      </c>
+      <c r="D91">
+        <v>0.479323996773455</v>
       </c>
       <c r="E91" t="s">
         <v>98</v>
-      </c>
-      <c r="F91" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2912,19 +2927,19 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>159</v>
+        <v>209</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D92" s="3">
-        <v>0.3</v>
+        <v>182</v>
+      </c>
+      <c r="D92">
+        <v>3.6477386676706303E-2</v>
       </c>
       <c r="E92" t="s">
         <v>98</v>
       </c>
-      <c r="F92" s="17">
-        <v>0.3</v>
+      <c r="F92" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2932,16 +2947,19 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D93" s="3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E93" t="s">
         <v>98</v>
+      </c>
+      <c r="F93" s="17">
+        <v>0.3</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -2949,18 +2967,35 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D94" s="3">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E94" t="s">
         <v>98</v>
       </c>
-      <c r="F94" t="s">
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" t="s">
+        <v>213</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D95">
+        <v>4.7651408708188597E-2</v>
+      </c>
+      <c r="E95" t="s">
+        <v>98</v>
+      </c>
+      <c r="F95" t="s">
         <v>212</v>
       </c>
     </row>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A989D643-F66B-42CD-9CF4-80E46D8709F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BE7C32-0C07-47B0-9A98-0F3B40E11737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2156,7 +2156,7 @@
         <v>243</v>
       </c>
       <c r="D46" s="16">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>98</v>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BE7C32-0C07-47B0-9A98-0F3B40E11737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADB9DC0-BA92-40B5-9DA4-DAF2580FD6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="247">
   <si>
     <t>category</t>
   </si>
@@ -778,6 +778,9 @@
   </si>
   <si>
     <t>cost reduction</t>
+  </si>
+  <si>
+    <t>not used, if bias corrected at micro calibration stage</t>
   </si>
 </sst>
 </file>
@@ -2885,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>26</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADB9DC0-BA92-40B5-9DA4-DAF2580FD6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129330EA-8F45-476A-8481-5A2561AFD5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="48" windowWidth="23016" windowHeight="12216" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="250">
   <si>
     <t>category</t>
   </si>
@@ -402,9 +402,6 @@
     <t>warmer_homes_introduction</t>
   </si>
   <si>
-    <t>retrofit hassle</t>
-  </si>
-  <si>
     <t>night rate electricity price discount</t>
   </si>
   <si>
@@ -591,9 +588,6 @@
     <t>eta.</t>
   </si>
   <si>
-    <t>for OSS the effective present bias is beta*eta.</t>
-  </si>
-  <si>
     <t>HLI threshold for heat pump support</t>
   </si>
   <si>
@@ -781,6 +775,21 @@
   </si>
   <si>
     <t>not used, if bias corrected at micro calibration stage</t>
+  </si>
+  <si>
+    <t>no rebound below this space heating requirement National Heat Study</t>
+  </si>
+  <si>
+    <t>Grant increase date</t>
+  </si>
+  <si>
+    <t>Grant increase factor</t>
+  </si>
+  <si>
+    <t>grant_increase_date</t>
+  </si>
+  <si>
+    <t>grant_increase_factor</t>
   </si>
 </sst>
 </file>
@@ -1296,48 +1305,48 @@
     </row>
     <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -1349,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1679-ADB0-42D7-8103-5D0EB0C9F50E}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -1419,13 +1428,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="D4" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1434,7 +1443,7 @@
         <v>98</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1445,7 +1454,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D5" s="8">
         <v>30</v>
@@ -1699,10 +1708,10 @@
         <v>29</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D20" s="8">
         <v>0</v>
@@ -1711,7 +1720,7 @@
         <v>23</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1719,10 +1728,10 @@
         <v>29</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D21" s="8">
         <v>0.3</v>
@@ -1731,7 +1740,7 @@
         <v>98</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1742,7 +1751,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D22" s="6">
         <v>2.25</v>
@@ -1759,7 +1768,7 @@
         <v>44</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" s="6">
         <v>2.75</v>
@@ -1768,7 +1777,7 @@
         <v>98</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1776,10 +1785,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="D24" s="6">
         <v>0.6</v>
@@ -1788,7 +1797,7 @@
         <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1796,10 +1805,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D25" s="6">
         <v>0.85</v>
@@ -1808,7 +1817,7 @@
         <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1816,10 +1825,10 @@
         <v>18</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D26" s="6">
         <v>0.9</v>
@@ -1836,7 +1845,7 @@
         <v>86</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D27" s="6">
         <v>0.75</v>
@@ -1853,7 +1862,7 @@
         <v>85</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D28" s="10">
         <v>1</v>
@@ -1952,10 +1961,10 @@
         <v>56</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="D34" s="10">
         <v>2.5</v>
@@ -1969,10 +1978,10 @@
         <v>56</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="D35" s="10">
         <v>2.5</v>
@@ -1986,10 +1995,10 @@
         <v>56</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D36" s="10">
         <v>1.5</v>
@@ -2003,10 +2012,10 @@
         <v>56</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D37" s="10">
         <v>3</v>
@@ -2020,10 +2029,10 @@
         <v>56</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D38" s="16">
         <v>2</v>
@@ -2037,16 +2046,16 @@
         <v>18</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D39" s="16">
         <v>15</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2054,16 +2063,16 @@
         <v>18</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D40" s="16">
         <v>30</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2071,16 +2080,16 @@
         <v>18</v>
       </c>
       <c r="B41" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>157</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>158</v>
       </c>
       <c r="D41" s="16">
         <v>8</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2088,19 +2097,19 @@
         <v>18</v>
       </c>
       <c r="B42" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="D42" s="16">
         <v>2.2999999999999998</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F42" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2108,10 +2117,10 @@
         <v>18</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D43" s="16">
         <v>1.25</v>
@@ -2123,10 +2132,10 @@
         <v>18</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D44" s="16">
         <v>1.1000000000000001</v>
@@ -2138,10 +2147,10 @@
         <v>18</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D45" s="16">
         <v>1.08</v>
@@ -2153,10 +2162,10 @@
         <v>18</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D46" s="16">
         <v>0.3</v>
@@ -2165,7 +2174,7 @@
         <v>98</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2173,10 +2182,10 @@
         <v>18</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D47" s="11">
         <v>0.6</v>
@@ -2185,7 +2194,7 @@
         <v>98</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2202,7 +2211,7 @@
         <v>11.8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2219,10 +2228,10 @@
         <v>12.8</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2239,7 +2248,7 @@
         <v>13.8</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2256,7 +2265,7 @@
         <v>16.8</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2273,7 +2282,7 @@
         <v>13.2</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2290,10 +2299,10 @@
         <v>14</v>
       </c>
       <c r="E53" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2310,7 +2319,7 @@
         <v>14.8</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2327,7 +2336,7 @@
         <v>17.2</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2344,7 +2353,7 @@
         <v>35.4</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6"/>
     </row>
@@ -2362,7 +2371,7 @@
         <v>35.4</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2379,7 +2388,7 @@
         <v>35.4</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2396,7 +2405,7 @@
         <v>35.4</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2404,10 +2413,10 @@
         <v>62</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D60" s="6">
         <v>0.4</v>
@@ -2419,10 +2428,10 @@
         <v>62</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D61" s="6">
         <v>0.4</v>
@@ -2434,10 +2443,10 @@
         <v>62</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D62" s="6">
         <v>0.4</v>
@@ -2449,10 +2458,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D63" s="6">
         <v>0.4</v>
@@ -2474,7 +2483,7 @@
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2492,7 +2501,7 @@
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2530,10 +2539,10 @@
         <v>6</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D68" s="14">
         <v>700</v>
@@ -2620,19 +2629,19 @@
         <v>6</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D74" s="14">
         <v>150</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2640,10 +2649,10 @@
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>239</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>241</v>
       </c>
       <c r="D75" s="14">
         <v>35000</v>
@@ -2658,19 +2667,19 @@
         <v>6</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D76" s="14">
         <v>2027</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2678,10 +2687,10 @@
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="D77" s="14">
         <v>2015.3</v>
@@ -2723,10 +2732,10 @@
         <v>6</v>
       </c>
       <c r="B80" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="13" t="s">
         <v>122</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>123</v>
       </c>
       <c r="D80" s="14">
         <v>2040</v>
@@ -2737,16 +2746,16 @@
         <v>6</v>
       </c>
       <c r="B81" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>199</v>
       </c>
       <c r="D81" s="14">
         <v>0.8</v>
       </c>
       <c r="E81" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2754,16 +2763,16 @@
         <v>6</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D82" s="14">
         <v>63.5</v>
       </c>
       <c r="E82" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2771,16 +2780,16 @@
         <v>6</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D83" s="14">
         <v>100</v>
       </c>
       <c r="E83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2788,90 +2797,84 @@
         <v>6</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D84" s="14">
         <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D85" s="14">
+        <v>2026.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D86" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="C87" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D87" s="19">
+        <v>3000</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B88" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D85" s="19">
-        <v>3000</v>
-      </c>
-      <c r="E85" t="s">
-        <v>23</v>
-      </c>
-      <c r="F85" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B86" s="19" t="s">
+      <c r="C88" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C86" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="D86" s="19">
-        <v>50</v>
-      </c>
-      <c r="E86" t="s">
-        <v>155</v>
-      </c>
-      <c r="F86" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D87">
-        <v>0.710843770010396</v>
-      </c>
-      <c r="E87" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>11</v>
-      </c>
-      <c r="B88" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88">
-        <v>1.14974246520316E-2</v>
+      <c r="D88" s="19">
+        <v>75</v>
       </c>
       <c r="E88" t="s">
-        <v>25</v>
+        <v>154</v>
+      </c>
+      <c r="F88" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2879,16 +2882,16 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" s="3">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="D89">
+        <v>0.594322503</v>
       </c>
       <c r="E89" t="s">
-        <v>246</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2896,16 +2899,16 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="D90">
-        <v>1.1404764768900301E-2</v>
+        <v>4.8274562E-2</v>
       </c>
       <c r="E90" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2913,16 +2916,16 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>117</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D91">
-        <v>0.479323996773455</v>
+        <v>16</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>98</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2930,19 +2933,16 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>209</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>182</v>
+        <v>10</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="D92">
-        <v>3.6477386676706303E-2</v>
+        <v>0.03</v>
       </c>
       <c r="E92" t="s">
-        <v>98</v>
-      </c>
-      <c r="F92" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2950,19 +2950,16 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D93" s="3">
-        <v>0.3</v>
+        <v>12</v>
+      </c>
+      <c r="D93">
+        <v>0.40077507600000001</v>
       </c>
       <c r="E93" t="s">
         <v>98</v>
-      </c>
-      <c r="F93" s="17">
-        <v>0.3</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -2970,16 +2967,19 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D94" s="3">
-        <v>0</v>
+        <v>181</v>
+      </c>
+      <c r="D94">
+        <v>0.12119928100000001</v>
       </c>
       <c r="E94" t="s">
         <v>98</v>
+      </c>
+      <c r="F94" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -2987,19 +2987,56 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="C95" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E95" t="s">
+        <v>98</v>
+      </c>
+      <c r="F95" s="17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" t="s">
         <v>211</v>
       </c>
-      <c r="D95">
-        <v>4.7651408708188597E-2</v>
-      </c>
-      <c r="E95" t="s">
-        <v>98</v>
-      </c>
-      <c r="F95" t="s">
-        <v>212</v>
+      <c r="C97" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D97">
+        <v>1.2961873E-2</v>
+      </c>
+      <c r="E97" t="s">
+        <v>98</v>
+      </c>
+      <c r="F97" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3009,8 +3046,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA1BE81-9C4C-49AE-A7FD-599BD867D62D}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="57.88671875" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3070,53 +3111,56 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="C5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="8">
         <v>30</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="7">
-        <v>40</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="8">
-        <v>60</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="7">
+        <v>40</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3128,7 +3172,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" s="8">
         <v>60</v>
@@ -3138,37 +3182,37 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="8">
+        <v>60</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D9" s="9">
         <v>60</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="5">
-        <v>700</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3176,25 +3220,27 @@
         <v>29</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5"/>
+        <v>700</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5">
         <v>0</v>
@@ -3202,36 +3248,34 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D13" s="7">
         <v>150</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="8">
-        <v>130</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3240,13 +3284,13 @@
         <v>29</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" s="8">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>7</v>
@@ -3257,53 +3301,50 @@
         <v>29</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" s="8">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="8">
+        <v>70</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D17" s="9">
         <v>120</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="8">
-        <v>110</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3311,19 +3352,19 @@
         <v>29</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="8">
         <v>110</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0.81</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>98</v>
+      <c r="E18" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -3331,19 +3372,19 @@
         <v>29</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D19" s="8">
-        <v>0</v>
+        <v>0.81</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>163</v>
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -3351,36 +3392,39 @@
         <v>29</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>173</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2.25</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -3394,13 +3438,10 @@
         <v>147</v>
       </c>
       <c r="D22" s="6">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="F22" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -3408,13 +3449,13 @@
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D23" s="6">
-        <v>0.6</v>
+        <v>2.75</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>98</v>
@@ -3428,13 +3469,13 @@
         <v>18</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="D24" s="6">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3448,16 +3489,19 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" t="s">
         <v>141</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -3465,50 +3509,50 @@
         <v>18</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="6">
         <v>0.75</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="10">
-        <v>1</v>
-      </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>46</v>
+        <v>149</v>
       </c>
       <c r="D28" s="10">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -3516,13 +3560,13 @@
         <v>56</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D29" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>9</v>
@@ -3533,13 +3577,13 @@
         <v>56</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D30" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>9</v>
@@ -3550,13 +3594,13 @@
         <v>56</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D31" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>9</v>
@@ -3567,13 +3611,13 @@
         <v>56</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D32" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>9</v>
@@ -3584,16 +3628,16 @@
         <v>56</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="D33" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>98</v>
+        <v>25</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3601,10 +3645,10 @@
         <v>56</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D34" s="10">
         <v>2.5</v>
@@ -3618,13 +3662,13 @@
         <v>56</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D35" s="10">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>98</v>
@@ -3638,47 +3682,47 @@
         <v>135</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D36" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="10">
         <v>3</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D37" s="16">
-        <v>2</v>
-      </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="16" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D38" s="16">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3686,16 +3730,16 @@
         <v>18</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D39" s="16">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -3703,16 +3747,16 @@
         <v>18</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D40" s="16">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -3720,19 +3764,16 @@
         <v>18</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="D41" s="16">
-        <v>2.2999999999999998</v>
+        <v>8</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="F41" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -3740,28 +3781,33 @@
         <v>18</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D42" s="16">
-        <v>1.25</v>
-      </c>
-      <c r="E42" s="16"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F42" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B43" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>193</v>
-      </c>
       <c r="D43" s="16">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="E43" s="16"/>
     </row>
@@ -3770,68 +3816,69 @@
         <v>18</v>
       </c>
       <c r="B44" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>194</v>
-      </c>
       <c r="D44" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="16">
         <v>1.08</v>
       </c>
-      <c r="E44" s="16"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
+      <c r="E45" s="16"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D45" s="11">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11.8</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>201</v>
+      <c r="B46" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>202</v>
+      <c r="A47" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3839,16 +3886,16 @@
         <v>62</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D48" s="6">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3859,13 +3906,16 @@
         <v>63</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D49" s="6">
-        <v>16.8</v>
+        <v>12.8</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3873,16 +3923,16 @@
         <v>62</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D50" s="6">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3890,19 +3940,16 @@
         <v>62</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D51" s="6">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -3913,13 +3960,13 @@
         <v>68</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D52" s="6">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -3930,12 +3977,15 @@
         <v>68</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D53" s="6">
-        <v>17.2</v>
+        <v>14</v>
       </c>
       <c r="E53" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F53" s="6" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3944,34 +3994,33 @@
         <v>62</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D54" s="6">
-        <v>35.4</v>
+        <v>14.8</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F54" s="6"/>
+        <v>199</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D55" s="6">
-        <v>35.4</v>
+        <v>17.2</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,14 +4031,15 @@
         <v>73</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D56" s="6">
         <v>35.4</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
@@ -3999,13 +4049,13 @@
         <v>73</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D57" s="6">
         <v>35.4</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4013,40 +4063,44 @@
         <v>62</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="D58" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E58" s="6"/>
+        <v>35.4</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="D59" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E59" s="6"/>
+        <v>35.4</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D60" s="6">
         <v>0.4</v>
@@ -4058,10 +4112,10 @@
         <v>62</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D61" s="6">
         <v>0.4</v>
@@ -4073,36 +4127,30 @@
         <v>62</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D62" s="6">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E62" s="6"/>
-      <c r="F62" s="6" t="s">
-        <v>204</v>
-      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D63" s="6">
-        <v>12.7</v>
+        <v>0.4</v>
       </c>
       <c r="E63" s="6"/>
-      <c r="F63" s="6" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
@@ -4112,99 +4160,107 @@
         <v>78</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D64" s="6">
-        <v>14</v>
+        <v>11.4</v>
       </c>
       <c r="E64" s="6"/>
+      <c r="F64" s="6" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C65" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="6">
+        <v>12.7</v>
+      </c>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="6">
+        <v>14</v>
+      </c>
+      <c r="E66" s="6"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D67" s="6">
         <v>17.899999999999999</v>
       </c>
-      <c r="E65" s="6"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D66" s="14">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D67" s="14">
-        <v>0.23</v>
-      </c>
+      <c r="E67" s="6"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B68" s="14" t="s">
-        <v>100</v>
+      <c r="B68" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>106</v>
+        <v>236</v>
       </c>
       <c r="D68" s="14">
-        <v>2018.3</v>
+        <v>700</v>
       </c>
       <c r="E68" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B69" s="14" t="s">
-        <v>101</v>
+      <c r="B69" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="D69" s="14">
-        <v>2022.15</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B70" s="14" t="s">
-        <v>118</v>
+      <c r="B70" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="D70" s="14">
-        <v>2011</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -4212,19 +4268,16 @@
         <v>6</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="D71" s="14">
-        <v>150</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F71" s="14" t="s">
-        <v>200</v>
+        <v>2018.3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -4232,16 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>177</v>
+        <v>101</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="D72" s="14">
-        <v>2025</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>180</v>
+        <v>2022.15</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -4249,13 +4299,13 @@
         <v>6</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D73" s="14">
-        <v>2015.3</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -4263,16 +4313,19 @@
         <v>6</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="D74" s="14">
-        <v>2024.3</v>
-      </c>
-      <c r="E74" t="s">
-        <v>104</v>
+        <v>150</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -4280,27 +4333,37 @@
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>109</v>
+        <v>237</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="D75" s="14">
-        <v>2040</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="14"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
       <c r="D76" s="14">
-        <v>2040</v>
+        <v>2027</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -4308,195 +4371,356 @@
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="14">
+        <v>2015.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" s="14">
+        <v>2024.3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D79" s="14">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80" s="14">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="C77" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="D77" s="14">
+      <c r="D81" s="14">
         <v>0.8</v>
       </c>
-      <c r="E77" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="18" t="s">
+      <c r="E81" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="D82" s="14">
+        <v>63.5</v>
+      </c>
+      <c r="E82" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D83" s="14">
+        <v>100</v>
+      </c>
+      <c r="E83" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="D84" s="14">
+        <v>200</v>
+      </c>
+      <c r="E84" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D85" s="14">
+        <v>2026.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D86" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="C87" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D87" s="19">
+        <v>3000</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B88" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C78" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D78" s="19">
-        <v>3000</v>
-      </c>
-      <c r="E78" t="s">
-        <v>23</v>
-      </c>
-      <c r="F78" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="19" t="s">
+      <c r="C88" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C79" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="D79" s="19">
-        <v>50</v>
-      </c>
-      <c r="E79" t="s">
-        <v>155</v>
-      </c>
-      <c r="F79" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="D88" s="19">
+        <v>75</v>
+      </c>
+      <c r="E88" t="s">
+        <v>154</v>
+      </c>
+      <c r="F88" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>11</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B89" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D80" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="D89">
+        <v>0.594322503</v>
+      </c>
+      <c r="E89" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>11</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B90" t="s">
         <v>17</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D81" s="3">
-        <v>2.2000000000000001E-3</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="D90">
+        <v>4.8274562E-2</v>
+      </c>
+      <c r="E90" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>11</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B91" t="s">
         <v>16</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E82" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="E91" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>11</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B92" t="s">
         <v>10</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D83" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="E83" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="C92" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92">
+        <v>0.03</v>
+      </c>
+      <c r="E92" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>11</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B93" t="s">
         <v>117</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C93" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="E84" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="D93">
+        <v>0.40077507600000001</v>
+      </c>
+      <c r="E93" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>11</v>
       </c>
-      <c r="B85" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="D85" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="E85" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="B94" t="s">
+        <v>207</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D94">
+        <v>0.12119928100000001</v>
+      </c>
+      <c r="E94" t="s">
+        <v>98</v>
+      </c>
+      <c r="F94" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>11</v>
       </c>
-      <c r="B86" t="s">
-        <v>159</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D86" s="3">
+      <c r="B95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="3">
         <v>0.3</v>
       </c>
-      <c r="E86" t="s">
-        <v>98</v>
-      </c>
-      <c r="F86" s="17">
+      <c r="E95" t="s">
+        <v>98</v>
+      </c>
+      <c r="F95" s="17">
         <v>0.3</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>11</v>
       </c>
-      <c r="B87" t="s">
-        <v>195</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D87" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E87" t="s">
-        <v>98</v>
+      <c r="B96" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" t="s">
+        <v>211</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D97">
+        <v>1.2961873E-2</v>
+      </c>
+      <c r="E97" t="s">
+        <v>98</v>
+      </c>
+      <c r="F97" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -4583,7 +4807,7 @@
         <v>30</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D4" s="8">
         <v>30</v>
@@ -4837,10 +5061,10 @@
         <v>29</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D19" s="8">
         <v>0</v>
@@ -4849,7 +5073,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -4857,10 +5081,10 @@
         <v>29</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D20" s="8">
         <v>0.3</v>
@@ -4869,7 +5093,7 @@
         <v>98</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -4880,7 +5104,7 @@
         <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D21" s="6">
         <v>2.25</v>
@@ -4897,7 +5121,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D22" s="6">
         <v>2.75</v>
@@ -4906,7 +5130,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -4914,10 +5138,10 @@
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="D23" s="6">
         <v>0.6</v>
@@ -4926,7 +5150,7 @@
         <v>98</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -4934,10 +5158,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" s="6">
         <v>0.85</v>
@@ -4946,7 +5170,7 @@
         <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -4954,10 +5178,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" s="6">
         <v>0.9</v>
@@ -4974,7 +5198,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D26" s="6">
         <v>0.75</v>
@@ -4991,7 +5215,7 @@
         <v>85</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D27" s="10">
         <v>1</v>
@@ -5090,10 +5314,10 @@
         <v>56</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="D33" s="10">
         <v>2.5</v>
@@ -5107,10 +5331,10 @@
         <v>56</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="D34" s="10">
         <v>2.5</v>
@@ -5124,10 +5348,10 @@
         <v>56</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D35" s="10">
         <v>1.5</v>
@@ -5141,10 +5365,10 @@
         <v>56</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" s="10">
         <v>3</v>
@@ -5158,10 +5382,10 @@
         <v>56</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D37" s="16">
         <v>2</v>
@@ -5175,16 +5399,16 @@
         <v>18</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D38" s="16">
         <v>15</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -5192,16 +5416,16 @@
         <v>18</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D39" s="16">
         <v>30</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -5209,16 +5433,16 @@
         <v>18</v>
       </c>
       <c r="B40" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="16" t="s">
         <v>157</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>158</v>
       </c>
       <c r="D40" s="16">
         <v>8</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -5226,19 +5450,19 @@
         <v>18</v>
       </c>
       <c r="B41" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>184</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="D41" s="16">
         <v>2</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -5246,10 +5470,10 @@
         <v>18</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D42" s="16">
         <v>1.25</v>
@@ -5261,10 +5485,10 @@
         <v>18</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D43" s="16">
         <v>1.1000000000000001</v>
@@ -5276,10 +5500,10 @@
         <v>18</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D44" s="16">
         <v>1.08</v>
@@ -5291,10 +5515,10 @@
         <v>18</v>
       </c>
       <c r="B45" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="11">
         <v>0</v>
@@ -5317,7 +5541,7 @@
         <v>11.8</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -5334,10 +5558,10 @@
         <v>12.8</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -5354,7 +5578,7 @@
         <v>13.8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -5371,7 +5595,7 @@
         <v>16.8</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -5388,7 +5612,7 @@
         <v>13.2</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -5405,10 +5629,10 @@
         <v>14</v>
       </c>
       <c r="E51" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -5425,7 +5649,7 @@
         <v>14.8</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -5442,7 +5666,7 @@
         <v>17.2</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -5459,7 +5683,7 @@
         <v>35.4</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6"/>
     </row>
@@ -5477,7 +5701,7 @@
         <v>35.4</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -5494,7 +5718,7 @@
         <v>35.4</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -5511,7 +5735,7 @@
         <v>35.4</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -5529,7 +5753,7 @@
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -5547,7 +5771,7 @@
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -5585,10 +5809,10 @@
         <v>62</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D62" s="6">
         <v>0.4</v>
@@ -5600,10 +5824,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D63" s="6">
         <v>0.4</v>
@@ -5615,10 +5839,10 @@
         <v>62</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D64" s="6">
         <v>0.4</v>
@@ -5630,10 +5854,10 @@
         <v>62</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D65" s="6">
         <v>0.4</v>
@@ -5718,19 +5942,19 @@
         <v>6</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D71" s="14">
         <v>150</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -5738,16 +5962,16 @@
         <v>6</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D72" s="14">
         <v>2025</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -5755,10 +5979,10 @@
         <v>6</v>
       </c>
       <c r="B73" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="D73" s="14">
         <v>2015.3</v>
@@ -5786,10 +6010,10 @@
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D75" s="14">
         <v>1</v>
@@ -5814,10 +6038,10 @@
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>122</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>123</v>
       </c>
       <c r="D77" s="14">
         <v>2040</v>
@@ -5828,27 +6052,27 @@
         <v>6</v>
       </c>
       <c r="B78" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C78" s="14" t="s">
         <v>197</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>199</v>
       </c>
       <c r="D78" s="14">
         <v>0.8</v>
       </c>
       <c r="E78" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B79" s="19" t="s">
-        <v>168</v>
-      </c>
       <c r="C79" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D79" s="19">
         <v>3000</v>
@@ -5857,27 +6081,27 @@
         <v>23</v>
       </c>
       <c r="F79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B80" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" s="19" t="s">
         <v>169</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>170</v>
       </c>
       <c r="D80" s="19">
         <v>50</v>
       </c>
       <c r="E80" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -5939,13 +6163,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D84" s="3">
         <v>0.04</v>
       </c>
       <c r="E84" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -5970,10 +6194,10 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D86" s="3">
         <v>0.02</v>
@@ -5982,7 +6206,7 @@
         <v>98</v>
       </c>
       <c r="F86" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -5990,10 +6214,10 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D87" s="3">
         <v>0.3</v>
@@ -6010,10 +6234,10 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D88" s="3">
         <v>0.1</v>
@@ -6027,10 +6251,10 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D89" s="3">
         <v>0.02</v>
@@ -6039,7 +6263,7 @@
         <v>98</v>
       </c>
       <c r="F89" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129330EA-8F45-476A-8481-5A2561AFD5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C339CC27-54AB-48B5-B03E-7DCB3C71AC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="48" windowWidth="23016" windowHeight="12216" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="251">
   <si>
     <t>category</t>
   </si>
@@ -790,6 +790,9 @@
   </si>
   <si>
     <t>grant_increase_factor</t>
+  </si>
+  <si>
+    <t>heat_pump_cop_2040</t>
   </si>
 </sst>
 </file>
@@ -3046,7 +3049,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA1BE81-9C4C-49AE-A7FD-599BD867D62D}">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="57.88671875" customWidth="1"/>
@@ -3469,19 +3472,16 @@
         <v>18</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="D24" s="6">
-        <v>0.6</v>
+        <v>3.25</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="F24" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -3492,16 +3492,16 @@
         <v>137</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D25" s="6">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -3512,13 +3512,16 @@
         <v>137</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D26" s="6">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
+      </c>
+      <c r="F26" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3526,50 +3529,50 @@
         <v>18</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D28" s="6">
         <v>0.75</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D28" s="10">
-        <v>1</v>
-      </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>46</v>
+        <v>149</v>
       </c>
       <c r="D29" s="10">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3577,13 +3580,13 @@
         <v>56</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D30" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>9</v>
@@ -3594,13 +3597,13 @@
         <v>56</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D31" s="10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>9</v>
@@ -3611,13 +3614,13 @@
         <v>56</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D32" s="10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>9</v>
@@ -3628,13 +3631,13 @@
         <v>56</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="D33" s="10">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>9</v>
@@ -3645,16 +3648,16 @@
         <v>56</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D34" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>98</v>
+        <v>25</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -3662,10 +3665,10 @@
         <v>56</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D35" s="10">
         <v>2.5</v>
@@ -3679,13 +3682,13 @@
         <v>56</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D36" s="10">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>98</v>
@@ -3696,50 +3699,50 @@
         <v>56</v>
       </c>
       <c r="B37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C38" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D38" s="10">
         <v>3</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="16">
-        <v>2</v>
-      </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D39" s="16">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -3747,13 +3750,13 @@
         <v>18</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D40" s="16">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>154</v>
@@ -3764,13 +3767,13 @@
         <v>18</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D41" s="16">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>154</v>
@@ -3781,19 +3784,16 @@
         <v>18</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="D42" s="16">
-        <v>2.2999999999999998</v>
+        <v>8</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F42" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -3801,28 +3801,33 @@
         <v>18</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D43" s="16">
-        <v>1.25</v>
-      </c>
-      <c r="E43" s="16"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F43" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D44" s="16">
-        <v>1.1000000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="E44" s="16"/>
     </row>
@@ -3831,13 +3836,13 @@
         <v>18</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D45" s="16">
-        <v>1.08</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E45" s="16"/>
     </row>
@@ -3846,56 +3851,54 @@
         <v>18</v>
       </c>
       <c r="B46" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D46" s="16">
+        <v>1.08</v>
+      </c>
+      <c r="E46" s="16"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D47" s="16">
         <v>0.3</v>
       </c>
-      <c r="E46" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F46" s="16" t="s">
+      <c r="E47" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="16" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B48" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C48" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D48" s="11">
         <v>0.6</v>
       </c>
-      <c r="E47" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F47" s="10" t="s">
+      <c r="E48" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>243</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" s="6">
-        <v>11.8</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -3903,19 +3906,16 @@
         <v>62</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D49" s="6">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3926,13 +3926,16 @@
         <v>63</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50" s="6">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>199</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -3943,10 +3946,10 @@
         <v>63</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D51" s="6">
-        <v>16.8</v>
+        <v>13.8</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>199</v>
@@ -3957,13 +3960,13 @@
         <v>62</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D52" s="6">
-        <v>13.2</v>
+        <v>16.8</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>199</v>
@@ -3977,16 +3980,13 @@
         <v>68</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D53" s="6">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -3997,13 +3997,16 @@
         <v>68</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D54" s="6">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -4014,10 +4017,10 @@
         <v>68</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D55" s="6">
-        <v>17.2</v>
+        <v>14.8</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>199</v>
@@ -4028,18 +4031,17 @@
         <v>62</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D56" s="6">
-        <v>35.4</v>
+        <v>17.2</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
@@ -4049,7 +4051,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D57" s="6">
         <v>35.4</v>
@@ -4057,6 +4059,7 @@
       <c r="E57" s="6" t="s">
         <v>199</v>
       </c>
+      <c r="F57" s="6"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
@@ -4066,7 +4069,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D58" s="6">
         <v>35.4</v>
@@ -4083,7 +4086,7 @@
         <v>73</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D59" s="6">
         <v>35.4</v>
@@ -4097,15 +4100,17 @@
         <v>62</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="D60" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E60" s="6"/>
+        <v>35.4</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
@@ -4115,7 +4120,7 @@
         <v>120</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D61" s="6">
         <v>0.4</v>
@@ -4130,7 +4135,7 @@
         <v>120</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D62" s="6">
         <v>0.4</v>
@@ -4145,7 +4150,7 @@
         <v>120</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D63" s="6">
         <v>0.4</v>
@@ -4157,18 +4162,15 @@
         <v>62</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D64" s="6">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="E64" s="6"/>
-      <c r="F64" s="6" t="s">
-        <v>202</v>
-      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
@@ -4178,14 +4180,14 @@
         <v>78</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D65" s="6">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -4196,57 +4198,61 @@
         <v>78</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D66" s="6">
-        <v>14</v>
+        <v>12.7</v>
       </c>
       <c r="E66" s="6"/>
+      <c r="F66" s="6" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C67" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67" s="6">
+        <v>14</v>
+      </c>
+      <c r="E67" s="6"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D68" s="6">
         <v>17.899999999999999</v>
       </c>
-      <c r="E67" s="6"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D68" s="14">
-        <v>700</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
+      <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="D69" s="14">
-        <v>0.13500000000000001</v>
+        <v>700</v>
+      </c>
+      <c r="E69" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -4254,30 +4260,27 @@
         <v>6</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D70" s="14">
-        <v>0.23</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B71" s="14" t="s">
-        <v>100</v>
+      <c r="B71" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="D71" s="14">
-        <v>2018.3</v>
-      </c>
-      <c r="E71" t="s">
-        <v>103</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -4285,13 +4288,16 @@
         <v>6</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D72" s="14">
-        <v>2022.15</v>
+        <v>2018.3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -4299,13 +4305,13 @@
         <v>6</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D73" s="14">
-        <v>2011</v>
+        <v>2022.15</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -4313,19 +4319,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="D74" s="14">
-        <v>150</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>198</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -4333,51 +4333,57 @@
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="D75" s="14">
-        <v>35000</v>
+        <v>150</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="14"/>
+        <v>154</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D76" s="14">
-        <v>2027</v>
+        <v>35000</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F76" s="14" t="s">
-        <v>238</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F76" s="14"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="D77" s="14">
-        <v>2015.3</v>
+        <v>2027</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -4385,16 +4391,13 @@
         <v>6</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D78" s="14">
-        <v>2024.3</v>
-      </c>
-      <c r="E78" t="s">
-        <v>104</v>
+        <v>2015.3</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -4402,13 +4405,16 @@
         <v>6</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D79" s="14">
-        <v>2040</v>
+        <v>2024.3</v>
+      </c>
+      <c r="E79" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -4416,10 +4422,10 @@
         <v>6</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D80" s="14">
         <v>2040</v>
@@ -4430,16 +4436,13 @@
         <v>6</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>197</v>
+        <v>121</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D81" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="E81" t="s">
-        <v>196</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -4447,16 +4450,16 @@
         <v>6</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="D82" s="14">
-        <v>63.5</v>
+        <v>0.8</v>
       </c>
       <c r="E82" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -4464,13 +4467,13 @@
         <v>6</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D83" s="14">
-        <v>100</v>
+        <v>63.5</v>
       </c>
       <c r="E83" t="s">
         <v>234</v>
@@ -4481,13 +4484,13 @@
         <v>6</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D84" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E84" t="s">
         <v>234</v>
@@ -4498,13 +4501,16 @@
         <v>6</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="D85" s="14">
-        <v>2026.5</v>
+        <v>200</v>
+      </c>
+      <c r="E85" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -4512,33 +4518,27 @@
         <v>6</v>
       </c>
       <c r="B86" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D86" s="14">
+        <v>2026.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C87" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D86" s="14">
+      <c r="D87" s="14">
         <v>1.5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D87" s="19">
-        <v>3000</v>
-      </c>
-      <c r="E87" t="s">
-        <v>23</v>
-      </c>
-      <c r="F87" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -4546,36 +4546,39 @@
         <v>166</v>
       </c>
       <c r="B88" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D88" s="19">
+        <v>3000</v>
+      </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C89" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D88" s="19">
+      <c r="D89" s="19">
         <v>75</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E89" t="s">
         <v>154</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F89" t="s">
         <v>245</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>11</v>
-      </c>
-      <c r="B89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D89">
-        <v>0.594322503</v>
-      </c>
-      <c r="E89" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -4583,13 +4586,13 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D90">
-        <v>4.8274562E-2</v>
+        <v>0.594322503</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
@@ -4600,16 +4603,16 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D91" s="3">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="D91">
+        <v>4.8274562E-2</v>
       </c>
       <c r="E91" t="s">
-        <v>244</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -4617,16 +4620,16 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D92">
-        <v>0.03</v>
+        <v>14</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -4634,16 +4637,16 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
-      </c>
-      <c r="C93" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="D93">
-        <v>0.40077507600000001</v>
+        <v>0.03</v>
       </c>
       <c r="E93" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -4651,19 +4654,16 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>181</v>
+        <v>12</v>
       </c>
       <c r="D94">
-        <v>0.12119928100000001</v>
+        <v>0.40077507600000001</v>
       </c>
       <c r="E94" t="s">
         <v>98</v>
-      </c>
-      <c r="F94" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -4671,19 +4671,19 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D95" s="3">
-        <v>0.3</v>
+        <v>181</v>
+      </c>
+      <c r="D95">
+        <v>0.12119928100000001</v>
       </c>
       <c r="E95" t="s">
         <v>98</v>
       </c>
-      <c r="F95" s="17">
-        <v>0.3</v>
+      <c r="F95" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -4691,16 +4691,19 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E96" t="s">
         <v>98</v>
+      </c>
+      <c r="F96" s="17">
+        <v>0.3</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -4708,18 +4711,35 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D97" s="3">
+        <v>0</v>
+      </c>
+      <c r="E97" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" t="s">
         <v>211</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C98" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="D97">
+      <c r="D98">
         <v>1.2961873E-2</v>
       </c>
-      <c r="E97" t="s">
-        <v>98</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="E98" t="s">
+        <v>98</v>
+      </c>
+      <c r="F98" t="s">
         <v>210</v>
       </c>
     </row>

--- a/inst/extdata/scenario_parameters.xlsx
+++ b/inst/extdata/scenario_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joe\pkgs\hpmicrosimr\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B441561-2ADA-4CF6-B8AD-BF030874A9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A892754F-4675-47D9-90DF-CF06678FEFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="288" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="204" windowWidth="23016" windowHeight="12216" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="7" r:id="rId1"/>
@@ -678,9 +678,6 @@
     <t>81.5k heat pump retrofits by 2019-2030</t>
   </si>
   <si>
-    <t>boiler ban from 2040, upgrade grants increase and maintained to 2040</t>
-  </si>
-  <si>
     <t>143k heat pump retrofits 2019-2030 120k DERs by 2030</t>
   </si>
   <si>
@@ -819,13 +816,16 @@
     <t>approximately 240k heat pump retrofits by 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">np pathway. Assumed measure are (1) 50% immediate increase in grants (2) 50% inncrease in warmer homes cost cap (3) relax HLI heat pump rule to 3.0 </t>
-  </si>
-  <si>
-    <t>CAP + oil boiler ban</t>
-  </si>
-  <si>
     <t>hit both emissions and EED sectoral target</t>
+  </si>
+  <si>
+    <t>(1) carbon price 200/tCO2 in 2030 (2) relax HLI rule to 3.0 in 2028 (3) ban new boilers in 2028 (4) 65% immediate increase in grant supports (5) warmers home deeper retrofits, cost cap at 50k</t>
+  </si>
+  <si>
+    <t>Assumed measures: (1) 60% immediate increase in grants (2) 50% increase in warmer homes cost effective cap to 45k and strict B2 (3) relax HLI heat pump rule to 2.8 in 3031 (4) oil boiler ban in 3031 (4) effective carbon price is doubled to 200t/CO2 in 2030 and 400t/CO2 in 2040</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (1) upgrade grants increased by 35% (2) warming homes cost cap increased to 45k and strict B2 in mide 2028. All other measures maintained to 2041</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2536B528-ACE0-4AEE-80FE-2144BA4A4410}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5546875" style="2" customWidth="1"/>
@@ -1358,10 +1358,10 @@
         <v>211</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>201</v>
       </c>
@@ -1369,13 +1369,13 @@
         <v>200</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>203</v>
       </c>
@@ -1383,13 +1383,13 @@
         <v>204</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
         <v>205</v>
       </c>
@@ -1397,13 +1397,10 @@
         <v>206</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D7" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1765,7 @@
         <v>91</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2139,7 +2136,7 @@
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2177,10 +2174,10 @@
         <v>18</v>
       </c>
       <c r="B43" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="D43" s="15">
         <v>0.3</v>
@@ -2189,7 +2186,7 @@
         <v>91</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2200,7 +2197,7 @@
         <v>143</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D44" s="10">
         <v>0.6</v>
@@ -2209,7 +2206,7 @@
         <v>91</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2552,10 +2549,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="D65" s="13">
         <v>700</v>
@@ -2662,10 +2659,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D72" s="13">
         <v>35000</v>
@@ -2692,7 +2689,7 @@
         <v>170</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2700,10 +2697,10 @@
         <v>6</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D74" s="13">
         <v>2041</v>
@@ -2716,16 +2713,16 @@
         <v>6</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D75" s="13">
         <v>120</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F75" s="13"/>
     </row>
@@ -2734,10 +2731,10 @@
         <v>6</v>
       </c>
       <c r="B76" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>253</v>
       </c>
       <c r="D76" s="13">
         <v>45000</v>
@@ -2828,10 +2825,10 @@
         <v>6</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D82" s="13">
         <v>15</v>
@@ -2842,16 +2839,16 @@
         <v>6</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D83" s="13">
         <v>63.5</v>
       </c>
       <c r="E83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2859,16 +2856,16 @@
         <v>6</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" s="13">
         <v>100</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2876,16 +2873,16 @@
         <v>6</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D85" s="13">
         <v>200</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -2893,10 +2890,10 @@
         <v>6</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D86" s="13">
         <v>2026.5</v>
@@ -2907,10 +2904,10 @@
         <v>6</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D87" s="13">
         <v>1</v>
@@ -2921,10 +2918,10 @@
         <v>6</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D88" s="13">
         <v>2041</v>
@@ -2935,10 +2932,10 @@
         <v>6</v>
       </c>
       <c r="B89" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="13" t="s">
         <v>236</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>237</v>
       </c>
       <c r="D89" s="13">
         <v>2041</v>
@@ -2952,7 +2949,7 @@
         <v>173</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D90" s="13">
         <v>2041</v>
@@ -2966,7 +2963,7 @@
         <v>173</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D91" s="13">
         <v>2.8</v>
@@ -2977,10 +2974,10 @@
         <v>6</v>
       </c>
       <c r="B92" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>248</v>
       </c>
       <c r="D92" s="13">
         <v>2041</v>
@@ -3023,7 +3020,7 @@
         <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3074,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3550,7 +3547,7 @@
         <v>91</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -3921,7 +3918,7 @@
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -3959,10 +3956,10 @@
         <v>18</v>
       </c>
       <c r="B43" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="D43" s="15">
         <v>0.3</v>
@@ -3971,7 +3968,7 @@
         <v>91</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3982,7 +3979,7 @@
         <v>143</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D44" s="10">
         <v>0.6</v>
@@ -3991,7 +3988,7 @@
         <v>91</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -4334,10 +4331,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="D65" s="13">
         <v>700</v>
@@ -4444,10 +4441,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D72" s="13">
         <v>35000</v>
@@ -4474,7 +4471,7 @@
         <v>170</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -4482,10 +4479,10 @@
         <v>6</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D74" s="13">
         <v>2028.5</v>
@@ -4498,16 +4495,16 @@
         <v>6</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D75" s="13">
         <v>120</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F75" s="13"/>
     </row>
@@ -4516,10 +4513,10 @@
         <v>6</v>
       </c>
       <c r="B76" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>253</v>
       </c>
       <c r="D76" s="13">
         <v>45000</v>
@@ -4610,10 +4607,10 @@
         <v>6</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D82" s="13">
         <v>15</v>
@@ -4624,16 +4621,16 @@
         <v>6</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D83" s="13">
         <v>63.5</v>
       </c>
       <c r="E83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -4641,16 +4638,16 @@
         <v>6</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" s="13">
         <v>100</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -4658,16 +4655,16 @@
         <v>6</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D85" s="13">
         <v>200</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -4675,10 +4672,10 @@
         <v>6</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D86" s="13">
         <v>2026.5</v>
@@ -4689,10 +4686,10 @@
         <v>6</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D87" s="13">
         <v>1.35</v>
@@ -4703,10 +4700,10 @@
         <v>6</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D88" s="13">
         <v>2041</v>
@@ -4717,10 +4714,10 @@
         <v>6</v>
       </c>
       <c r="B89" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="13" t="s">
         <v>236</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>237</v>
       </c>
       <c r="D89" s="13">
         <v>2041</v>
@@ -4734,7 +4731,7 @@
         <v>173</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D90" s="13">
         <v>2041</v>
@@ -4748,10 +4745,10 @@
         <v>173</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D91" s="13">
-        <v>2.8</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -4759,10 +4756,10 @@
         <v>6</v>
       </c>
       <c r="B92" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>248</v>
       </c>
       <c r="D92" s="13">
         <v>2041</v>
@@ -4805,7 +4802,7 @@
         <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -4856,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -5332,7 +5329,7 @@
         <v>91</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -5703,7 +5700,7 @@
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -5741,10 +5738,10 @@
         <v>18</v>
       </c>
       <c r="B43" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="D43" s="15">
         <v>0.3</v>
@@ -5753,7 +5750,7 @@
         <v>91</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -5764,7 +5761,7 @@
         <v>143</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D44" s="10">
         <v>0.6</v>
@@ -5773,7 +5770,7 @@
         <v>91</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -6116,10 +6113,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="D65" s="13">
         <v>700</v>
@@ -6226,10 +6223,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D72" s="13">
         <v>35000</v>
@@ -6256,7 +6253,7 @@
         <v>170</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -6264,13 +6261,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D74" s="13">
-        <v>2041</v>
+        <v>2028.5</v>
       </c>
       <c r="E74" s="13"/>
       <c r="F74" s="13"/>
@@ -6280,16 +6277,16 @@
         <v>6</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D75" s="13">
         <v>120</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F75" s="13"/>
     </row>
@@ -6298,10 +6295,10 @@
         <v>6</v>
       </c>
       <c r="B76" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>253</v>
       </c>
       <c r="D76" s="13">
         <v>45000</v>
@@ -6392,10 +6389,10 @@
         <v>6</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D82" s="13">
         <v>15</v>
@@ -6406,16 +6403,16 @@
         <v>6</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D83" s="13">
         <v>63.5</v>
       </c>
       <c r="E83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -6423,16 +6420,16 @@
         <v>6</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" s="13">
         <v>100</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -6440,16 +6437,16 @@
         <v>6</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D85" s="13">
         <v>200</v>
       </c>
       <c r="E85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -6457,10 +6454,10 @@
         <v>6</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D86" s="13">
         <v>2026.5</v>
@@ -6471,13 +6468,13 @@
         <v>6</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D87" s="13">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -6485,13 +6482,13 @@
         <v>6</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D88" s="13">
-        <v>2041</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -6499,10 +6496,10 @@
         <v>6</v>
       </c>
       <c r="B89" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="13" t="s">
         <v>236</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>237</v>
       </c>
       <c r="D89" s="13">
         <v>2041</v>
@@ -6516,10 +6513,10 @@
         <v>173</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D90" s="13">
-        <v>2041</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -6530,7 +6527,7 @@
         <v>173</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D91" s="13">
         <v>2.8</v>
@@ -6541,13 +6538,13 @@
         <v>6</v>
       </c>
       <c r="B92" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>248</v>
-      </c>
       <c r="D92" s="13">
-        <v>2041</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -6587,7 +6584,7 @@
         <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -6638,7 +6635,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -7114,7 +7111,7 @@
         <v>91</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -7485,7 +7482,7 @@
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -7523,10 +7520,10 @@
         <v>18</v>
       </c>
       <c r="B43" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="D43" s="15">
         <v>0.3</v>
@@ -7535,7 +7532,7 @@
         <v>91</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -7546,7 +7543,7 @@
         <v>143</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D44" s="10">
         <v>0.6</v>
@@ -7555,7 +7552,7 @@
         <v>91</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -7898,10 +7895,10 @@
         <v>6</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>220</v>
       </c>
       <c r="D65" s="13">
         <v>700</v>
@@ -8008,10 +8005,10 @@
         <v>6</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D72" s="13">
         <v>35000</v>
@@ -8038,7 +8035,7 @@
         <v>170</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -8046,13 +8043,13 @@
         <v>6</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D74" s="13">
-        <v>2041</v>
+        <v>2028</v>
       </c>
       <c r="E74" s="13"/>
       <c r="F74" s="13"/>
@@ -8062,16 +8059,16 @@
         <v>6</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D75" s="13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F75" s="13"/>
     </row>
@@ -8080,13 +8077,13 @@
         <v>6</v>
       </c>
       <c r="B76" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>253</v>
-      </c>
       <c r="D76" s="13">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>23</v>
@@ -8174,10 +8171,10 @@
         <v>6</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D82" s="13">
         <v>15</v>
@@ -8188,16 +8185,16 @@
         <v>6</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D83" s="13">
         <v>63.5</v>
       </c>
       <c r="E83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -8205,16 +8202,16 @@
         <v>6</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" s="13">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -8222,16 +8219,16 @@
         <v>6</v>
       </c>
       <c r="B85" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D85" s="13">
+        <v>400</v>
+      </c>
+      <c r="E85" t="s">
         <v>217</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="D85" s="13">
-        <v>200</v>
-      </c>
-      <c r="E85" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -8239,10 +8236,10 @@
         <v>6</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D86" s="13">
         <v>2026.5</v>
@@ -8253,13 +8250,13 @@
         <v>6</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D87" s="13">
-        <v>1</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -8267,13 +8264,13 @@
         <v>6</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D88" s="13">
-        <v>2041</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -8281,13 +8278,13 @@
         <v>6</v>
       </c>
       <c r="B89" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C89" s="13" t="s">
-        <v>237</v>
-      </c>
       <c r="D89" s="13">
-        <v>2041</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -8298,10 +8295,10 @@
         <v>173</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D90" s="13">
-        <v>2041</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -8312,10 +8309,10 @@
         <v>173</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D91" s="13">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -8323,13 +8320,13 @@
         <v>6</v>
       </c>
       <c r="B92" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C92" s="13" t="s">
-        <v>248</v>
-      </c>
       <c r="D92" s="13">
-        <v>2041</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -8369,7 +8366,7 @@
         <v>146</v>
       </c>
       <c r="F94" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -8420,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
